--- a/data-analytics/testing/Emergency_Contact_Testing_Tracker_482.xlsx
+++ b/data-analytics/testing/Emergency_Contact_Testing_Tracker_482.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Emergency Contact Tests" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Emergency Contact Tests'!$A$4:$K$63</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Emergency Contact Tests'!$A$4:$K$157</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K63"/>
+  <dimension ref="A1:K157"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -549,7 +549,7 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>SECTION 1: Country-Level Default Contacts (sample of 73 countries)</t>
+          <t>SECTION 1: Country-Level Default Contacts (all 73 countries)</t>
         </is>
       </c>
     </row>
@@ -559,12 +559,12 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Afghanistan</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>AF</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
@@ -576,12 +576,24 @@
       <c r="F6" s="5" t="inlineStr"/>
       <c r="G6" s="5" t="inlineStr">
         <is>
-          <t>General Emergency: 911, Police: 911, Ambulance: 911, Fire: 911, Suicide Helpline: 988</t>
-        </is>
-      </c>
-      <c r="H6" s="5" t="inlineStr"/>
-      <c r="I6" s="5" t="inlineStr"/>
-      <c r="J6" s="5" t="inlineStr"/>
+          <t>Police: 119, Ambulance: 112, Fire: 119</t>
+        </is>
+      </c>
+      <c r="H6" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="I6" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="J6" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
       <c r="K6" s="5" t="inlineStr"/>
     </row>
     <row r="7">
@@ -590,12 +602,12 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Argentina</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
@@ -607,12 +619,24 @@
       <c r="F7" s="5" t="inlineStr"/>
       <c r="G7" s="5" t="inlineStr">
         <is>
-          <t>General Emergency: 112, Police: 112, Ambulance: 108, Fire: 101, Disaster Management: 108, Women Helpline: 1091, Suicide Helpline: 9152987821</t>
-        </is>
-      </c>
-      <c r="H7" s="5" t="inlineStr"/>
-      <c r="I7" s="5" t="inlineStr"/>
-      <c r="J7" s="5" t="inlineStr"/>
+          <t>Police: 911, Ambulance: 911, Fire: 911</t>
+        </is>
+      </c>
+      <c r="H7" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="I7" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="J7" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
       <c r="K7" s="5" t="inlineStr"/>
     </row>
     <row r="8">
@@ -621,12 +645,12 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
@@ -638,12 +662,24 @@
       <c r="F8" s="5" t="inlineStr"/>
       <c r="G8" s="5" t="inlineStr">
         <is>
-          <t>General Emergency: 999, Police: 999, Ambulance: 999, Fire: 999</t>
-        </is>
-      </c>
-      <c r="H8" s="5" t="inlineStr"/>
-      <c r="I8" s="5" t="inlineStr"/>
-      <c r="J8" s="5" t="inlineStr"/>
+          <t>General Emergency: 000, Police: 000, Ambulance: 000, Fire: 000</t>
+        </is>
+      </c>
+      <c r="H8" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="I8" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="J8" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
       <c r="K8" s="5" t="inlineStr"/>
     </row>
     <row r="9">
@@ -652,12 +688,12 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Bangladesh</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>BD</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
@@ -669,12 +705,24 @@
       <c r="F9" s="5" t="inlineStr"/>
       <c r="G9" s="5" t="inlineStr">
         <is>
-          <t>General Emergency: 911, Police: 911, Ambulance: 911, Fire: 911</t>
-        </is>
-      </c>
-      <c r="H9" s="5" t="inlineStr"/>
-      <c r="I9" s="5" t="inlineStr"/>
-      <c r="J9" s="5" t="inlineStr"/>
+          <t>Police: 999, Ambulance: 999, Fire: 999</t>
+        </is>
+      </c>
+      <c r="H9" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="I9" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="J9" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
       <c r="K9" s="5" t="inlineStr"/>
     </row>
     <row r="10">
@@ -683,12 +731,12 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Belgium</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
@@ -700,12 +748,24 @@
       <c r="F10" s="5" t="inlineStr"/>
       <c r="G10" s="5" t="inlineStr">
         <is>
-          <t>General Emergency: 000, Police: 000, Ambulance: 000, Fire: 000</t>
-        </is>
-      </c>
-      <c r="H10" s="5" t="inlineStr"/>
-      <c r="I10" s="5" t="inlineStr"/>
-      <c r="J10" s="5" t="inlineStr"/>
+          <t>General Emergency: 112, Police: 101, Ambulance: 112, Fire: 112</t>
+        </is>
+      </c>
+      <c r="H10" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="I10" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="J10" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
       <c r="K10" s="5" t="inlineStr"/>
     </row>
     <row r="11">
@@ -714,12 +774,12 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Bulgaria</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>BG</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
@@ -731,12 +791,24 @@
       <c r="F11" s="5" t="inlineStr"/>
       <c r="G11" s="5" t="inlineStr">
         <is>
-          <t>General Emergency: 112, Police: 110, Ambulance: 112, Fire: 112</t>
-        </is>
-      </c>
-      <c r="H11" s="5" t="inlineStr"/>
-      <c r="I11" s="5" t="inlineStr"/>
-      <c r="J11" s="5" t="inlineStr"/>
+          <t>Police: 112, Ambulance: 112, Fire: 112</t>
+        </is>
+      </c>
+      <c r="H11" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="I11" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="J11" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
       <c r="K11" s="5" t="inlineStr"/>
     </row>
     <row r="12">
@@ -745,12 +817,12 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>BR</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
@@ -762,12 +834,24 @@
       <c r="F12" s="5" t="inlineStr"/>
       <c r="G12" s="5" t="inlineStr">
         <is>
-          <t>Police: 112, Ambulance: 112, Fire: 112</t>
-        </is>
-      </c>
-      <c r="H12" s="5" t="inlineStr"/>
-      <c r="I12" s="5" t="inlineStr"/>
-      <c r="J12" s="5" t="inlineStr"/>
+          <t>Police: 190, Ambulance: 192, Fire: 193</t>
+        </is>
+      </c>
+      <c r="H12" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="I12" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="J12" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
       <c r="K12" s="5" t="inlineStr"/>
     </row>
     <row r="13">
@@ -776,12 +860,12 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
@@ -793,12 +877,24 @@
       <c r="F13" s="5" t="inlineStr"/>
       <c r="G13" s="5" t="inlineStr">
         <is>
-          <t>Police: 110, Ambulance: 119, Fire: 119</t>
-        </is>
-      </c>
-      <c r="H13" s="5" t="inlineStr"/>
-      <c r="I13" s="5" t="inlineStr"/>
-      <c r="J13" s="5" t="inlineStr"/>
+          <t>General Emergency: 911, Police: 911, Ambulance: 911, Fire: 911</t>
+        </is>
+      </c>
+      <c r="H13" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="I13" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="J13" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
       <c r="K13" s="5" t="inlineStr"/>
     </row>
     <row r="14">
@@ -807,12 +903,12 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Switzerland</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
@@ -824,12 +920,24 @@
       <c r="F14" s="5" t="inlineStr"/>
       <c r="G14" s="5" t="inlineStr">
         <is>
-          <t>Police: 190, Ambulance: 192, Fire: 193</t>
-        </is>
-      </c>
-      <c r="H14" s="5" t="inlineStr"/>
-      <c r="I14" s="5" t="inlineStr"/>
-      <c r="J14" s="5" t="inlineStr"/>
+          <t>General Emergency: 112, Police: 117, Ambulance: 144, Fire: 118</t>
+        </is>
+      </c>
+      <c r="H14" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="I14" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="J14" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
       <c r="K14" s="5" t="inlineStr"/>
     </row>
     <row r="15">
@@ -838,12 +946,12 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>Chile</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>MX</t>
+          <t>CL</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
@@ -855,12 +963,24 @@
       <c r="F15" s="5" t="inlineStr"/>
       <c r="G15" s="5" t="inlineStr">
         <is>
-          <t>Police: 911, Ambulance: 911, Fire: 911</t>
-        </is>
-      </c>
-      <c r="H15" s="5" t="inlineStr"/>
-      <c r="I15" s="5" t="inlineStr"/>
-      <c r="J15" s="5" t="inlineStr"/>
+          <t>Police: 133, Ambulance: 131, Fire: 132</t>
+        </is>
+      </c>
+      <c r="H15" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="I15" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="J15" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
       <c r="K15" s="5" t="inlineStr"/>
     </row>
     <row r="16">
@@ -869,12 +989,12 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>South Africa</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>ZA</t>
+          <t>CO</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
@@ -886,12 +1006,24 @@
       <c r="F16" s="5" t="inlineStr"/>
       <c r="G16" s="5" t="inlineStr">
         <is>
-          <t>Police: 10 111, Ambulance: 10 177, Fire: 10 177</t>
-        </is>
-      </c>
-      <c r="H16" s="5" t="inlineStr"/>
-      <c r="I16" s="5" t="inlineStr"/>
-      <c r="J16" s="5" t="inlineStr"/>
+          <t>Police: 123, Ambulance: 123, Fire: 123</t>
+        </is>
+      </c>
+      <c r="H16" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="I16" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="J16" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
       <c r="K16" s="5" t="inlineStr"/>
     </row>
     <row r="17">
@@ -900,12 +1032,12 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>Nigeria</t>
+          <t>Czech Republic</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>NG</t>
+          <t>CZ</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
@@ -920,9 +1052,21 @@
           <t>Police: 112, Ambulance: 112, Fire: 112</t>
         </is>
       </c>
-      <c r="H17" s="5" t="inlineStr"/>
-      <c r="I17" s="5" t="inlineStr"/>
-      <c r="J17" s="5" t="inlineStr"/>
+      <c r="H17" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="I17" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="J17" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
       <c r="K17" s="5" t="inlineStr"/>
     </row>
     <row r="18">
@@ -931,12 +1075,12 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>EG</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
@@ -948,12 +1092,24 @@
       <c r="F18" s="5" t="inlineStr"/>
       <c r="G18" s="5" t="inlineStr">
         <is>
-          <t>Police: 112, Ambulance: 123, Fire: 180</t>
-        </is>
-      </c>
-      <c r="H18" s="5" t="inlineStr"/>
-      <c r="I18" s="5" t="inlineStr"/>
-      <c r="J18" s="5" t="inlineStr"/>
+          <t>General Emergency: 112, Police: 110, Ambulance: 112, Fire: 112</t>
+        </is>
+      </c>
+      <c r="H18" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="I18" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="J18" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
       <c r="K18" s="5" t="inlineStr"/>
     </row>
     <row r="19">
@@ -962,12 +1118,12 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>Pakistan</t>
+          <t>Denmark</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>PK</t>
+          <t>DK</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
@@ -979,12 +1135,24 @@
       <c r="F19" s="5" t="inlineStr"/>
       <c r="G19" s="5" t="inlineStr">
         <is>
-          <t>Police: 15, Ambulance: 1122, Fire: 16</t>
-        </is>
-      </c>
-      <c r="H19" s="5" t="inlineStr"/>
-      <c r="I19" s="5" t="inlineStr"/>
-      <c r="J19" s="5" t="inlineStr"/>
+          <t>Police: 112, Ambulance: 112, Fire: 112</t>
+        </is>
+      </c>
+      <c r="H19" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="I19" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="J19" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
       <c r="K19" s="5" t="inlineStr"/>
     </row>
     <row r="20">
@@ -993,12 +1161,12 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>Bangladesh</t>
+          <t>Algeria</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>BD</t>
+          <t>DZ</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
@@ -1010,12 +1178,24 @@
       <c r="F20" s="5" t="inlineStr"/>
       <c r="G20" s="5" t="inlineStr">
         <is>
-          <t>Police: 999, Ambulance: 999, Fire: 999</t>
-        </is>
-      </c>
-      <c r="H20" s="5" t="inlineStr"/>
-      <c r="I20" s="5" t="inlineStr"/>
-      <c r="J20" s="5" t="inlineStr"/>
+          <t>Police: 1548, Ambulance: 14, Fire: 14</t>
+        </is>
+      </c>
+      <c r="H20" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="I20" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="J20" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
       <c r="K20" s="5" t="inlineStr"/>
     </row>
     <row r="21">
@@ -1024,12 +1204,12 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Egypt</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
@@ -1041,12 +1221,24 @@
       <c r="F21" s="5" t="inlineStr"/>
       <c r="G21" s="5" t="inlineStr">
         <is>
-          <t>Police: 999, Ambulance: 995, Fire: 995</t>
-        </is>
-      </c>
-      <c r="H21" s="5" t="inlineStr"/>
-      <c r="I21" s="5" t="inlineStr"/>
-      <c r="J21" s="5" t="inlineStr"/>
+          <t>Police: 112, Ambulance: 123, Fire: 180</t>
+        </is>
+      </c>
+      <c r="H21" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="I21" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="J21" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
       <c r="K21" s="5" t="inlineStr"/>
     </row>
     <row r="22">
@@ -1055,12 +1247,12 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>Spain</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>NZ</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
@@ -1072,12 +1264,24 @@
       <c r="F22" s="5" t="inlineStr"/>
       <c r="G22" s="5" t="inlineStr">
         <is>
-          <t>General Emergency: 111, Police: 111, Ambulance: 111, Fire: 111</t>
-        </is>
-      </c>
-      <c r="H22" s="5" t="inlineStr"/>
-      <c r="I22" s="5" t="inlineStr"/>
-      <c r="J22" s="5" t="inlineStr"/>
+          <t>Police: 112, Ambulance: 112, Fire: 112</t>
+        </is>
+      </c>
+      <c r="H22" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="I22" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="J22" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
       <c r="K22" s="5" t="inlineStr"/>
     </row>
     <row r="23">
@@ -1086,12 +1290,12 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>Ethiopia</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>CH</t>
+          <t>ET</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
@@ -1103,12 +1307,24 @@
       <c r="F23" s="5" t="inlineStr"/>
       <c r="G23" s="5" t="inlineStr">
         <is>
-          <t>General Emergency: 112, Police: 117, Ambulance: 144, Fire: 118</t>
-        </is>
-      </c>
-      <c r="H23" s="5" t="inlineStr"/>
-      <c r="I23" s="5" t="inlineStr"/>
-      <c r="J23" s="5" t="inlineStr"/>
+          <t>Police: 911, Ambulance: 911, Fire: 911</t>
+        </is>
+      </c>
+      <c r="H23" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="I23" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="J23" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
       <c r="K23" s="5" t="inlineStr"/>
     </row>
     <row r="24">
@@ -1117,12 +1333,12 @@
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>Greece</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>GR</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
@@ -1134,12 +1350,24 @@
       <c r="F24" s="5" t="inlineStr"/>
       <c r="G24" s="5" t="inlineStr">
         <is>
-          <t>General Emergency: 112, Police: 100, Ambulance: 166, Fire: 199</t>
-        </is>
-      </c>
-      <c r="H24" s="5" t="inlineStr"/>
-      <c r="I24" s="5" t="inlineStr"/>
-      <c r="J24" s="5" t="inlineStr"/>
+          <t>Police: 112, Ambulance: 112, Fire: 112</t>
+        </is>
+      </c>
+      <c r="H24" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="I24" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="J24" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
       <c r="K24" s="5" t="inlineStr"/>
     </row>
     <row r="25">
@@ -1148,12 +1376,12 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>Poland</t>
+          <t>France</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
@@ -1165,229 +1393,373 @@
       <c r="F25" s="5" t="inlineStr"/>
       <c r="G25" s="5" t="inlineStr">
         <is>
-          <t>General Emergency: 112, Police: 997, Ambulance: 999, Fire: 998</t>
-        </is>
-      </c>
-      <c r="H25" s="5" t="inlineStr"/>
-      <c r="I25" s="5" t="inlineStr"/>
-      <c r="J25" s="5" t="inlineStr"/>
+          <t>Police: 112, Ambulance: 112, Fire: 112</t>
+        </is>
+      </c>
+      <c r="H25" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="I25" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="J25" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
       <c r="K25" s="5" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="4" t="inlineStr">
-        <is>
-          <t>SECTION 2: India — State-Level Contacts</t>
-        </is>
-      </c>
+      <c r="A26" s="5" t="n">
+        <v>21</v>
+      </c>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>GB</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="inlineStr">
+        <is>
+          <t>(default)</t>
+        </is>
+      </c>
+      <c r="E26" s="5" t="inlineStr"/>
+      <c r="F26" s="5" t="inlineStr"/>
+      <c r="G26" s="5" t="inlineStr">
+        <is>
+          <t>General Emergency: 999, Police: 999, Ambulance: 999, Fire: 999</t>
+        </is>
+      </c>
+      <c r="H26" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="I26" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="J26" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="K26" s="5" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="5" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Ghana</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>GH</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>Karnataka</t>
+          <t>(default)</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr"/>
       <c r="F27" s="5" t="inlineStr"/>
       <c r="G27" s="5" t="inlineStr">
         <is>
-          <t>Police: 112, Ambulance: 108, Fire: 101</t>
-        </is>
-      </c>
-      <c r="H27" s="5" t="inlineStr"/>
-      <c r="I27" s="5" t="inlineStr"/>
-      <c r="J27" s="5" t="inlineStr"/>
+          <t>Police: 112, Ambulance: 112, Fire: 112</t>
+        </is>
+      </c>
+      <c r="H27" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="I27" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="J27" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
       <c r="K27" s="5" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="5" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Greece</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>GR</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>Maharashtra</t>
+          <t>(default)</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr"/>
       <c r="F28" s="5" t="inlineStr"/>
       <c r="G28" s="5" t="inlineStr">
         <is>
-          <t>Police: 112, Ambulance: 108, Fire: 101</t>
-        </is>
-      </c>
-      <c r="H28" s="5" t="inlineStr"/>
-      <c r="I28" s="5" t="inlineStr"/>
-      <c r="J28" s="5" t="inlineStr"/>
+          <t>General Emergency: 112, Police: 100, Ambulance: 166, Fire: 199</t>
+        </is>
+      </c>
+      <c r="H28" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="I28" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="J28" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
       <c r="K28" s="5" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="5" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Croatia</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>Tamil Nadu</t>
+          <t>(default)</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr"/>
       <c r="F29" s="5" t="inlineStr"/>
       <c r="G29" s="5" t="inlineStr">
         <is>
-          <t>Police: 112, Ambulance: 108, Fire: 101</t>
-        </is>
-      </c>
-      <c r="H29" s="5" t="inlineStr"/>
-      <c r="I29" s="5" t="inlineStr"/>
-      <c r="J29" s="5" t="inlineStr"/>
+          <t>Police: 112, Ambulance: 112, Fire: 112</t>
+        </is>
+      </c>
+      <c r="H29" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="I29" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="J29" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
       <c r="K29" s="5" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="4" t="inlineStr">
-        <is>
-          <t>SECTION 3: India — City-Level Contacts</t>
-        </is>
-      </c>
+      <c r="A30" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>Hungary</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>HU</t>
+        </is>
+      </c>
+      <c r="D30" s="5" t="inlineStr">
+        <is>
+          <t>(default)</t>
+        </is>
+      </c>
+      <c r="E30" s="5" t="inlineStr"/>
+      <c r="F30" s="5" t="inlineStr"/>
+      <c r="G30" s="5" t="inlineStr">
+        <is>
+          <t>Police: 112, Ambulance: 112, Fire: 112</t>
+        </is>
+      </c>
+      <c r="H30" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="I30" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="J30" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="K30" s="5" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="5" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Indonesia</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>ID</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>Karnataka</t>
+          <t>(default)</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr"/>
-      <c r="F31" s="5" t="inlineStr">
-        <is>
-          <t>Bengaluru</t>
-        </is>
-      </c>
+      <c r="F31" s="5" t="inlineStr"/>
       <c r="G31" s="5" t="inlineStr">
         <is>
-          <t>Police: 112, Ambulance: 108</t>
-        </is>
-      </c>
-      <c r="H31" s="5" t="inlineStr"/>
-      <c r="I31" s="5" t="inlineStr"/>
-      <c r="J31" s="5" t="inlineStr"/>
+          <t>Police: 112, Ambulance: 112, Fire: 112</t>
+        </is>
+      </c>
+      <c r="H31" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="I31" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="J31" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
       <c r="K31" s="5" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="5" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Ireland</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>IE</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>Karnataka</t>
+          <t>(default)</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr"/>
-      <c r="F32" s="5" t="inlineStr">
-        <is>
-          <t>Mysuru</t>
-        </is>
-      </c>
+      <c r="F32" s="5" t="inlineStr"/>
       <c r="G32" s="5" t="inlineStr">
         <is>
-          <t>Police: 112, Ambulance: 108</t>
-        </is>
-      </c>
-      <c r="H32" s="5" t="inlineStr"/>
-      <c r="I32" s="5" t="inlineStr"/>
-      <c r="J32" s="5" t="inlineStr"/>
+          <t>Police: 112, Ambulance: 112, Fire: 112</t>
+        </is>
+      </c>
+      <c r="H32" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="I32" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="J32" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
       <c r="K32" s="5" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="5" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Israel</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>IL</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>Karnataka</t>
+          <t>(default)</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr"/>
-      <c r="F33" s="5" t="inlineStr">
-        <is>
-          <t>Tumakuru</t>
-        </is>
-      </c>
+      <c r="F33" s="5" t="inlineStr"/>
       <c r="G33" s="5" t="inlineStr">
         <is>
-          <t>Police: 112, Ambulance: 108</t>
-        </is>
-      </c>
-      <c r="H33" s="5" t="inlineStr"/>
-      <c r="I33" s="5" t="inlineStr"/>
-      <c r="J33" s="5" t="inlineStr"/>
+          <t>Police: 100, Ambulance: 101, Fire: 102</t>
+        </is>
+      </c>
+      <c r="H33" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="I33" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="J33" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
       <c r="K33" s="5" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="5" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
@@ -1401,876 +1773,5450 @@
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>Karnataka</t>
+          <t>(default)</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr"/>
-      <c r="F34" s="5" t="inlineStr">
-        <is>
-          <t>Hubli</t>
-        </is>
-      </c>
+      <c r="F34" s="5" t="inlineStr"/>
       <c r="G34" s="5" t="inlineStr">
         <is>
-          <t>Police: 112, Ambulance: 108</t>
-        </is>
-      </c>
-      <c r="H34" s="5" t="inlineStr"/>
-      <c r="I34" s="5" t="inlineStr"/>
-      <c r="J34" s="5" t="inlineStr"/>
+          <t>General Emergency: 112, Police: 112, Ambulance: 108, Fire: 101, Disaster Management: 108, Women Helpline: 1091, Suicide Helpline: 9152987821</t>
+        </is>
+      </c>
+      <c r="H34" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="I34" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="J34" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
       <c r="K34" s="5" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="5" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Iraq</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>IQ</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>Maharashtra</t>
+          <t>(default)</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr"/>
-      <c r="F35" s="5" t="inlineStr">
-        <is>
-          <t>Mumbai</t>
-        </is>
-      </c>
+      <c r="F35" s="5" t="inlineStr"/>
       <c r="G35" s="5" t="inlineStr">
         <is>
-          <t>Police: 112, Ambulance: 108</t>
-        </is>
-      </c>
-      <c r="H35" s="5" t="inlineStr"/>
-      <c r="I35" s="5" t="inlineStr"/>
-      <c r="J35" s="5" t="inlineStr"/>
+          <t>Police: 112, Ambulance: 112, Fire: 112</t>
+        </is>
+      </c>
+      <c r="H35" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="I35" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="J35" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
       <c r="K35" s="5" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="5" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Iran</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>IR</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>Maharashtra</t>
+          <t>(default)</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr"/>
-      <c r="F36" s="5" t="inlineStr">
-        <is>
-          <t>Pune</t>
-        </is>
-      </c>
+      <c r="F36" s="5" t="inlineStr"/>
       <c r="G36" s="5" t="inlineStr">
         <is>
-          <t>Police: 112, Ambulance: 108</t>
-        </is>
-      </c>
-      <c r="H36" s="5" t="inlineStr"/>
-      <c r="I36" s="5" t="inlineStr"/>
-      <c r="J36" s="5" t="inlineStr"/>
+          <t>Police: 110, Ambulance: 115, Fire: 125</t>
+        </is>
+      </c>
+      <c r="H36" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="I36" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="J36" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
       <c r="K36" s="5" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="5" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Italy</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>Tamil Nadu</t>
+          <t>(default)</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr"/>
-      <c r="F37" s="5" t="inlineStr">
-        <is>
-          <t>Chennai</t>
-        </is>
-      </c>
+      <c r="F37" s="5" t="inlineStr"/>
       <c r="G37" s="5" t="inlineStr">
         <is>
-          <t>Police: 112, Ambulance: 108</t>
-        </is>
-      </c>
-      <c r="H37" s="5" t="inlineStr"/>
-      <c r="I37" s="5" t="inlineStr"/>
-      <c r="J37" s="5" t="inlineStr"/>
+          <t>Police: 112, Ambulance: 112, Fire: 112</t>
+        </is>
+      </c>
+      <c r="H37" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="I37" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="J37" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
       <c r="K37" s="5" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="4" t="inlineStr">
-        <is>
-          <t>SECTION 4: India — ZIP-Level Contacts</t>
-        </is>
-      </c>
+      <c r="A38" s="5" t="n">
+        <v>33</v>
+      </c>
+      <c r="B38" s="5" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="D38" s="5" t="inlineStr">
+        <is>
+          <t>(default)</t>
+        </is>
+      </c>
+      <c r="E38" s="5" t="inlineStr"/>
+      <c r="F38" s="5" t="inlineStr"/>
+      <c r="G38" s="5" t="inlineStr">
+        <is>
+          <t>Police: 110, Ambulance: 119, Fire: 119</t>
+        </is>
+      </c>
+      <c r="H38" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="I38" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="J38" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="K38" s="5" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="5" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Kenya</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>KE</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>Karnataka</t>
+          <t>(default)</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr"/>
-      <c r="F39" s="5" t="inlineStr">
-        <is>
-          <t>560001</t>
-        </is>
-      </c>
+      <c r="F39" s="5" t="inlineStr"/>
       <c r="G39" s="5" t="inlineStr">
         <is>
-          <t>Police: 112, Ambulance: 108</t>
-        </is>
-      </c>
-      <c r="H39" s="5" t="inlineStr"/>
-      <c r="I39" s="5" t="inlineStr"/>
-      <c r="J39" s="5" t="inlineStr"/>
+          <t>Police: 112, Ambulance: 112, Fire: 112</t>
+        </is>
+      </c>
+      <c r="H39" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="I39" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="J39" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
       <c r="K39" s="5" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="5" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Cambodia</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>KH</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>Karnataka</t>
+          <t>(default)</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr"/>
-      <c r="F40" s="5" t="inlineStr">
-        <is>
-          <t>560002</t>
-        </is>
-      </c>
+      <c r="F40" s="5" t="inlineStr"/>
       <c r="G40" s="5" t="inlineStr">
         <is>
-          <t>Police: 112, Ambulance: 108</t>
-        </is>
-      </c>
-      <c r="H40" s="5" t="inlineStr"/>
-      <c r="I40" s="5" t="inlineStr"/>
-      <c r="J40" s="5" t="inlineStr"/>
+          <t>Police: 117, Ambulance: 119, Fire: 118</t>
+        </is>
+      </c>
+      <c r="H40" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="I40" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="J40" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
       <c r="K40" s="5" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="5" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Kazakhstan</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>KZ</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>Karnataka</t>
+          <t>(default)</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr"/>
-      <c r="F41" s="5" t="inlineStr">
-        <is>
-          <t>572103</t>
-        </is>
-      </c>
+      <c r="F41" s="5" t="inlineStr"/>
       <c r="G41" s="5" t="inlineStr">
         <is>
-          <t>Police: 112, Ambulance: 108</t>
-        </is>
-      </c>
-      <c r="H41" s="5" t="inlineStr"/>
-      <c r="I41" s="5" t="inlineStr"/>
-      <c r="J41" s="5" t="inlineStr"/>
+          <t>Police: 112, Ambulance: 112, Fire: 112</t>
+        </is>
+      </c>
+      <c r="H41" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="I41" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="J41" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
       <c r="K41" s="5" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="4" t="inlineStr">
-        <is>
-          <t>SECTION 5: US — State-Level Contacts (sample)</t>
-        </is>
-      </c>
+      <c r="A42" s="5" t="n">
+        <v>37</v>
+      </c>
+      <c r="B42" s="5" t="inlineStr">
+        <is>
+          <t>Laos</t>
+        </is>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>LA</t>
+        </is>
+      </c>
+      <c r="D42" s="5" t="inlineStr">
+        <is>
+          <t>(default)</t>
+        </is>
+      </c>
+      <c r="E42" s="5" t="inlineStr"/>
+      <c r="F42" s="5" t="inlineStr"/>
+      <c r="G42" s="5" t="inlineStr">
+        <is>
+          <t>Police: 191, Ambulance: 195, Fire: 190</t>
+        </is>
+      </c>
+      <c r="H42" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="I42" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="J42" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="K42" s="5" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="5" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Sri Lanka</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>LK</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>California</t>
+          <t>(default)</t>
         </is>
       </c>
       <c r="E43" s="5" t="inlineStr"/>
       <c r="F43" s="5" t="inlineStr"/>
       <c r="G43" s="5" t="inlineStr">
         <is>
-          <t>Police: 911, Ambulance: 911, Fire: 911, Suicide Helpline: 988</t>
-        </is>
-      </c>
-      <c r="H43" s="5" t="inlineStr"/>
-      <c r="I43" s="5" t="inlineStr"/>
-      <c r="J43" s="5" t="inlineStr"/>
+          <t>Police: 119, Ambulance: 110, Fire: 110</t>
+        </is>
+      </c>
+      <c r="H43" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="I43" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="J43" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
       <c r="K43" s="5" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="5" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Morocco</t>
         </is>
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>New York</t>
+          <t>(default)</t>
         </is>
       </c>
       <c r="E44" s="5" t="inlineStr"/>
       <c r="F44" s="5" t="inlineStr"/>
       <c r="G44" s="5" t="inlineStr">
         <is>
-          <t>Police: 911, Ambulance: 911, Fire: 911, Suicide Helpline: 988</t>
-        </is>
-      </c>
-      <c r="H44" s="5" t="inlineStr"/>
-      <c r="I44" s="5" t="inlineStr"/>
-      <c r="J44" s="5" t="inlineStr"/>
+          <t>Police: 19, Ambulance: 15, Fire: 15</t>
+        </is>
+      </c>
+      <c r="H44" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="I44" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="J44" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
       <c r="K44" s="5" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="5" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Myanmar</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>MM</t>
         </is>
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>Texas</t>
+          <t>(default)</t>
         </is>
       </c>
       <c r="E45" s="5" t="inlineStr"/>
       <c r="F45" s="5" t="inlineStr"/>
       <c r="G45" s="5" t="inlineStr">
         <is>
-          <t>Police: 911, Ambulance: 911, Fire: 911, Suicide Helpline: 988</t>
-        </is>
-      </c>
-      <c r="H45" s="5" t="inlineStr"/>
-      <c r="I45" s="5" t="inlineStr"/>
-      <c r="J45" s="5" t="inlineStr"/>
+          <t>Police: 999, Ambulance: 999, Fire: 999</t>
+        </is>
+      </c>
+      <c r="H45" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="I45" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="J45" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
       <c r="K45" s="5" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="5" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Mongolia</t>
         </is>
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>MN</t>
         </is>
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>Florida</t>
+          <t>(default)</t>
         </is>
       </c>
       <c r="E46" s="5" t="inlineStr"/>
       <c r="F46" s="5" t="inlineStr"/>
       <c r="G46" s="5" t="inlineStr">
         <is>
-          <t>Police: 911, Ambulance: 911, Fire: 911, Suicide Helpline: 988</t>
-        </is>
-      </c>
-      <c r="H46" s="5" t="inlineStr"/>
-      <c r="I46" s="5" t="inlineStr"/>
-      <c r="J46" s="5" t="inlineStr"/>
+          <t>Police: 105, Ambulance: 105, Fire: 105</t>
+        </is>
+      </c>
+      <c r="H46" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="I46" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="J46" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
       <c r="K46" s="5" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="5" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Macau</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>MO</t>
         </is>
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>Illinois</t>
+          <t>(default)</t>
         </is>
       </c>
       <c r="E47" s="5" t="inlineStr"/>
       <c r="F47" s="5" t="inlineStr"/>
       <c r="G47" s="5" t="inlineStr">
         <is>
-          <t>Police: 911, Ambulance: 911, Fire: 911, Suicide Helpline: 988</t>
-        </is>
-      </c>
-      <c r="H47" s="5" t="inlineStr"/>
-      <c r="I47" s="5" t="inlineStr"/>
-      <c r="J47" s="5" t="inlineStr"/>
+          <t>Police: 999, Ambulance: 999, Fire: 999</t>
+        </is>
+      </c>
+      <c r="H47" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="I47" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="J47" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
       <c r="K47" s="5" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="5" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Mexico</t>
         </is>
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>MX</t>
         </is>
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>Pennsylvania</t>
+          <t>(default)</t>
         </is>
       </c>
       <c r="E48" s="5" t="inlineStr"/>
       <c r="F48" s="5" t="inlineStr"/>
       <c r="G48" s="5" t="inlineStr">
         <is>
-          <t>Police: 911, Ambulance: 911, Fire: 911, Suicide Helpline: 988</t>
-        </is>
-      </c>
-      <c r="H48" s="5" t="inlineStr"/>
-      <c r="I48" s="5" t="inlineStr"/>
-      <c r="J48" s="5" t="inlineStr"/>
+          <t>Police: 911, Ambulance: 911, Fire: 911</t>
+        </is>
+      </c>
+      <c r="H48" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="I48" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="J48" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
       <c r="K48" s="5" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="5" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Malaysia</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>MY</t>
         </is>
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
-          <t>Ohio</t>
+          <t>(default)</t>
         </is>
       </c>
       <c r="E49" s="5" t="inlineStr"/>
       <c r="F49" s="5" t="inlineStr"/>
       <c r="G49" s="5" t="inlineStr">
         <is>
-          <t>Police: 911, Ambulance: 911, Fire: 911, Suicide Helpline: 988</t>
-        </is>
-      </c>
-      <c r="H49" s="5" t="inlineStr"/>
-      <c r="I49" s="5" t="inlineStr"/>
-      <c r="J49" s="5" t="inlineStr"/>
+          <t>Police: 999, Ambulance: 999, Fire: 999</t>
+        </is>
+      </c>
+      <c r="H49" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="I49" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="J49" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
       <c r="K49" s="5" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="5" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="B50" s="5" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Nigeria</t>
         </is>
       </c>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>NG</t>
         </is>
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
-          <t>Arizona</t>
+          <t>(default)</t>
         </is>
       </c>
       <c r="E50" s="5" t="inlineStr"/>
       <c r="F50" s="5" t="inlineStr"/>
       <c r="G50" s="5" t="inlineStr">
         <is>
-          <t>Police: 911, Ambulance: 911, Fire: 911, Suicide Helpline: 988</t>
-        </is>
-      </c>
-      <c r="H50" s="5" t="inlineStr"/>
-      <c r="I50" s="5" t="inlineStr"/>
-      <c r="J50" s="5" t="inlineStr"/>
+          <t>Police: 112, Ambulance: 112, Fire: 112</t>
+        </is>
+      </c>
+      <c r="H50" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="I50" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="J50" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
       <c r="K50" s="5" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="5" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>NL</t>
         </is>
       </c>
       <c r="D51" s="5" t="inlineStr">
         <is>
-          <t>Colorado</t>
+          <t>(default)</t>
         </is>
       </c>
       <c r="E51" s="5" t="inlineStr"/>
       <c r="F51" s="5" t="inlineStr"/>
       <c r="G51" s="5" t="inlineStr">
         <is>
-          <t>Police: 911, Ambulance: 911, Fire: 911, Suicide Helpline: 988</t>
-        </is>
-      </c>
-      <c r="H51" s="5" t="inlineStr"/>
-      <c r="I51" s="5" t="inlineStr"/>
-      <c r="J51" s="5" t="inlineStr"/>
+          <t>Police: 112, Ambulance: 112, Fire: 112</t>
+        </is>
+      </c>
+      <c r="H51" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="I51" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="J51" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
       <c r="K51" s="5" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="5" t="n">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="B52" s="5" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>Puerto Rico</t>
+          <t>(default)</t>
         </is>
       </c>
       <c r="E52" s="5" t="inlineStr"/>
       <c r="F52" s="5" t="inlineStr"/>
       <c r="G52" s="5" t="inlineStr">
         <is>
-          <t>Police: 911, Ambulance: 911, Fire: 911, Suicide Helpline: 988</t>
-        </is>
-      </c>
-      <c r="H52" s="5" t="inlineStr"/>
-      <c r="I52" s="5" t="inlineStr"/>
-      <c r="J52" s="5" t="inlineStr"/>
+          <t>Police: 112, Ambulance: 113, Fire: 110</t>
+        </is>
+      </c>
+      <c r="H52" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="I52" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="J52" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
       <c r="K52" s="5" t="inlineStr"/>
     </row>
     <row r="53">
-      <c r="A53" s="4" t="inlineStr">
-        <is>
-          <t>SECTION 6: US — City-Level Contacts</t>
-        </is>
-      </c>
+      <c r="A53" s="5" t="n">
+        <v>48</v>
+      </c>
+      <c r="B53" s="5" t="inlineStr">
+        <is>
+          <t>Nepal</t>
+        </is>
+      </c>
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t>NP</t>
+        </is>
+      </c>
+      <c r="D53" s="5" t="inlineStr">
+        <is>
+          <t>(default)</t>
+        </is>
+      </c>
+      <c r="E53" s="5" t="inlineStr"/>
+      <c r="F53" s="5" t="inlineStr"/>
+      <c r="G53" s="5" t="inlineStr">
+        <is>
+          <t>Police: 100, Ambulance: 102, Fire: 101</t>
+        </is>
+      </c>
+      <c r="H53" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="I53" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="J53" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="K53" s="5" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="5" t="n">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="B54" s="5" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="C54" s="5" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>NZ</t>
         </is>
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
-          <t>California</t>
+          <t>(default)</t>
         </is>
       </c>
       <c r="E54" s="5" t="inlineStr"/>
-      <c r="F54" s="5" t="inlineStr">
-        <is>
-          <t>Los Angeles</t>
-        </is>
-      </c>
+      <c r="F54" s="5" t="inlineStr"/>
       <c r="G54" s="5" t="inlineStr">
         <is>
-          <t>Police: 911, Ambulance: 911, Fire: 911</t>
-        </is>
-      </c>
-      <c r="H54" s="5" t="inlineStr"/>
-      <c r="I54" s="5" t="inlineStr"/>
-      <c r="J54" s="5" t="inlineStr"/>
+          <t>General Emergency: 111, Police: 111, Ambulance: 111, Fire: 111</t>
+        </is>
+      </c>
+      <c r="H54" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="I54" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="J54" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
       <c r="K54" s="5" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="5" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Peru</t>
         </is>
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>PE</t>
         </is>
       </c>
       <c r="D55" s="5" t="inlineStr">
         <is>
-          <t>California</t>
+          <t>(default)</t>
         </is>
       </c>
       <c r="E55" s="5" t="inlineStr"/>
-      <c r="F55" s="5" t="inlineStr">
-        <is>
-          <t>San Francisco</t>
-        </is>
-      </c>
+      <c r="F55" s="5" t="inlineStr"/>
       <c r="G55" s="5" t="inlineStr">
         <is>
           <t>Police: 911, Ambulance: 911, Fire: 911</t>
         </is>
       </c>
-      <c r="H55" s="5" t="inlineStr"/>
-      <c r="I55" s="5" t="inlineStr"/>
-      <c r="J55" s="5" t="inlineStr"/>
+      <c r="H55" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="I55" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="J55" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
       <c r="K55" s="5" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="5" t="n">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="B56" s="5" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Philippines</t>
         </is>
       </c>
       <c r="C56" s="5" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="D56" s="5" t="inlineStr">
         <is>
-          <t>California</t>
+          <t>(default)</t>
         </is>
       </c>
       <c r="E56" s="5" t="inlineStr"/>
-      <c r="F56" s="5" t="inlineStr">
-        <is>
-          <t>San Diego</t>
-        </is>
-      </c>
+      <c r="F56" s="5" t="inlineStr"/>
       <c r="G56" s="5" t="inlineStr">
         <is>
           <t>Police: 911, Ambulance: 911, Fire: 911</t>
         </is>
       </c>
-      <c r="H56" s="5" t="inlineStr"/>
-      <c r="I56" s="5" t="inlineStr"/>
-      <c r="J56" s="5" t="inlineStr"/>
+      <c r="H56" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="I56" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="J56" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
       <c r="K56" s="5" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="5" t="n">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Pakistan</t>
         </is>
       </c>
       <c r="C57" s="5" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>PK</t>
         </is>
       </c>
       <c r="D57" s="5" t="inlineStr">
         <is>
-          <t>California</t>
+          <t>(default)</t>
         </is>
       </c>
       <c r="E57" s="5" t="inlineStr"/>
-      <c r="F57" s="5" t="inlineStr">
-        <is>
-          <t>San Jose</t>
-        </is>
-      </c>
+      <c r="F57" s="5" t="inlineStr"/>
       <c r="G57" s="5" t="inlineStr">
         <is>
-          <t>Police: 911, Ambulance: 911, Fire: 911</t>
-        </is>
-      </c>
-      <c r="H57" s="5" t="inlineStr"/>
-      <c r="I57" s="5" t="inlineStr"/>
-      <c r="J57" s="5" t="inlineStr"/>
+          <t>Police: 15, Ambulance: 1122, Fire: 16</t>
+        </is>
+      </c>
+      <c r="H57" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="I57" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="J57" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
       <c r="K57" s="5" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="5" t="n">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="B58" s="5" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Poland</t>
         </is>
       </c>
       <c r="C58" s="5" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="D58" s="5" t="inlineStr">
         <is>
-          <t>New York</t>
+          <t>(default)</t>
         </is>
       </c>
       <c r="E58" s="5" t="inlineStr"/>
-      <c r="F58" s="5" t="inlineStr">
-        <is>
-          <t>New York</t>
-        </is>
-      </c>
+      <c r="F58" s="5" t="inlineStr"/>
       <c r="G58" s="5" t="inlineStr">
         <is>
-          <t>Police: 911, Ambulance: 911, Fire: 911</t>
-        </is>
-      </c>
-      <c r="H58" s="5" t="inlineStr"/>
-      <c r="I58" s="5" t="inlineStr"/>
-      <c r="J58" s="5" t="inlineStr"/>
+          <t>General Emergency: 112, Police: 997, Ambulance: 999, Fire: 998</t>
+        </is>
+      </c>
+      <c r="H58" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="I58" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="J58" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
       <c r="K58" s="5" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="5" t="n">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="B59" s="5" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="C59" s="5" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="D59" s="5" t="inlineStr">
         <is>
-          <t>New York</t>
+          <t>(default)</t>
         </is>
       </c>
       <c r="E59" s="5" t="inlineStr"/>
-      <c r="F59" s="5" t="inlineStr">
-        <is>
-          <t>Buffalo</t>
-        </is>
-      </c>
+      <c r="F59" s="5" t="inlineStr"/>
       <c r="G59" s="5" t="inlineStr">
         <is>
-          <t>Police: 911, Ambulance: 911, Fire: 911</t>
-        </is>
-      </c>
-      <c r="H59" s="5" t="inlineStr"/>
-      <c r="I59" s="5" t="inlineStr"/>
-      <c r="J59" s="5" t="inlineStr"/>
+          <t>Police: 112, Ambulance: 112, Fire: 112</t>
+        </is>
+      </c>
+      <c r="H59" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="I59" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="J59" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
       <c r="K59" s="5" t="inlineStr"/>
     </row>
     <row r="60">
-      <c r="A60" s="4" t="inlineStr">
-        <is>
-          <t>SECTION 7: Edge Cases</t>
-        </is>
-      </c>
+      <c r="A60" s="5" t="n">
+        <v>55</v>
+      </c>
+      <c r="B60" s="5" t="inlineStr">
+        <is>
+          <t>Romania</t>
+        </is>
+      </c>
+      <c r="C60" s="5" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="D60" s="5" t="inlineStr">
+        <is>
+          <t>(default)</t>
+        </is>
+      </c>
+      <c r="E60" s="5" t="inlineStr"/>
+      <c r="F60" s="5" t="inlineStr"/>
+      <c r="G60" s="5" t="inlineStr">
+        <is>
+          <t>Police: 112, Ambulance: 112, Fire: 112</t>
+        </is>
+      </c>
+      <c r="H60" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="I60" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="J60" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="K60" s="5" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="5" t="n">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="B61" s="5" t="inlineStr">
         <is>
-          <t>Unknown country code</t>
+          <t>Serbia</t>
         </is>
       </c>
       <c r="C61" s="5" t="inlineStr">
         <is>
-          <t>XX</t>
-        </is>
-      </c>
-      <c r="D61" s="5" t="inlineStr"/>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="D61" s="5" t="inlineStr">
+        <is>
+          <t>(default)</t>
+        </is>
+      </c>
       <c r="E61" s="5" t="inlineStr"/>
       <c r="F61" s="5" t="inlineStr"/>
       <c r="G61" s="5" t="inlineStr">
         <is>
-          <t>Should show error or fallback</t>
-        </is>
-      </c>
-      <c r="H61" s="5" t="inlineStr"/>
-      <c r="I61" s="5" t="inlineStr"/>
-      <c r="J61" s="5" t="inlineStr"/>
+          <t>General Emergency: 112, Police: 192, Ambulance: 194, Fire: 193</t>
+        </is>
+      </c>
+      <c r="H61" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="I61" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="J61" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
       <c r="K61" s="5" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="5" t="n">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="B62" s="5" t="inlineStr">
         <is>
-          <t>Missing location data</t>
-        </is>
-      </c>
-      <c r="C62" s="5" t="inlineStr"/>
-      <c r="D62" s="5" t="inlineStr"/>
+          <t>Russia</t>
+        </is>
+      </c>
+      <c r="C62" s="5" t="inlineStr">
+        <is>
+          <t>RU</t>
+        </is>
+      </c>
+      <c r="D62" s="5" t="inlineStr">
+        <is>
+          <t>(default)</t>
+        </is>
+      </c>
       <c r="E62" s="5" t="inlineStr"/>
       <c r="F62" s="5" t="inlineStr"/>
       <c r="G62" s="5" t="inlineStr">
         <is>
-          <t>Page should not crash</t>
-        </is>
-      </c>
-      <c r="H62" s="5" t="inlineStr"/>
-      <c r="I62" s="5" t="inlineStr"/>
-      <c r="J62" s="5" t="inlineStr"/>
+          <t>General Emergency: 112, Police: 102, Ambulance: 103, Fire: 101</t>
+        </is>
+      </c>
+      <c r="H62" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="I62" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="J62" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
       <c r="K62" s="5" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="5" t="n">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="B63" s="5" t="inlineStr">
         <is>
-          <t>Country with no state data</t>
+          <t>Saudi Arabia</t>
         </is>
       </c>
       <c r="C63" s="5" t="inlineStr">
         <is>
-          <t>AF</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="D63" s="5" t="inlineStr">
         <is>
-          <t>Afghanistan</t>
+          <t>(default)</t>
         </is>
       </c>
       <c r="E63" s="5" t="inlineStr"/>
       <c r="F63" s="5" t="inlineStr"/>
       <c r="G63" s="5" t="inlineStr">
         <is>
+          <t>Police: 911, Ambulance: 911, Fire: 911</t>
+        </is>
+      </c>
+      <c r="H63" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="I63" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="J63" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="K63" s="5" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="5" t="n">
+        <v>59</v>
+      </c>
+      <c r="B64" s="5" t="inlineStr">
+        <is>
+          <t>Sweden</t>
+        </is>
+      </c>
+      <c r="C64" s="5" t="inlineStr">
+        <is>
+          <t>SE</t>
+        </is>
+      </c>
+      <c r="D64" s="5" t="inlineStr">
+        <is>
+          <t>(default)</t>
+        </is>
+      </c>
+      <c r="E64" s="5" t="inlineStr"/>
+      <c r="F64" s="5" t="inlineStr"/>
+      <c r="G64" s="5" t="inlineStr">
+        <is>
+          <t>Police: 112, Ambulance: 112, Fire: 112</t>
+        </is>
+      </c>
+      <c r="H64" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="I64" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="J64" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="K64" s="5" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="5" t="n">
+        <v>60</v>
+      </c>
+      <c r="B65" s="5" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="C65" s="5" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="D65" s="5" t="inlineStr">
+        <is>
+          <t>(default)</t>
+        </is>
+      </c>
+      <c r="E65" s="5" t="inlineStr"/>
+      <c r="F65" s="5" t="inlineStr"/>
+      <c r="G65" s="5" t="inlineStr">
+        <is>
+          <t>Police: 999, Ambulance: 995, Fire: 995</t>
+        </is>
+      </c>
+      <c r="H65" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="I65" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="J65" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="K65" s="5" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="5" t="n">
+        <v>61</v>
+      </c>
+      <c r="B66" s="5" t="inlineStr">
+        <is>
+          <t>Slovenia</t>
+        </is>
+      </c>
+      <c r="C66" s="5" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="D66" s="5" t="inlineStr">
+        <is>
+          <t>(default)</t>
+        </is>
+      </c>
+      <c r="E66" s="5" t="inlineStr"/>
+      <c r="F66" s="5" t="inlineStr"/>
+      <c r="G66" s="5" t="inlineStr">
+        <is>
+          <t>Police: 112, Ambulance: 112, Fire: 112</t>
+        </is>
+      </c>
+      <c r="H66" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="I66" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="J66" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="K66" s="5" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="5" t="n">
+        <v>62</v>
+      </c>
+      <c r="B67" s="5" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="C67" s="5" t="inlineStr">
+        <is>
+          <t>SK</t>
+        </is>
+      </c>
+      <c r="D67" s="5" t="inlineStr">
+        <is>
+          <t>(default)</t>
+        </is>
+      </c>
+      <c r="E67" s="5" t="inlineStr"/>
+      <c r="F67" s="5" t="inlineStr"/>
+      <c r="G67" s="5" t="inlineStr">
+        <is>
+          <t>General Emergency: 112, Police: 158, Ambulance: 155, Fire: 150</t>
+        </is>
+      </c>
+      <c r="H67" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="I67" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="J67" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="K67" s="5" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="5" t="n">
+        <v>63</v>
+      </c>
+      <c r="B68" s="5" t="inlineStr">
+        <is>
+          <t>Thailand</t>
+        </is>
+      </c>
+      <c r="C68" s="5" t="inlineStr">
+        <is>
+          <t>TH</t>
+        </is>
+      </c>
+      <c r="D68" s="5" t="inlineStr">
+        <is>
+          <t>(default)</t>
+        </is>
+      </c>
+      <c r="E68" s="5" t="inlineStr"/>
+      <c r="F68" s="5" t="inlineStr"/>
+      <c r="G68" s="5" t="inlineStr">
+        <is>
+          <t>Police: 191, Ambulance: 1669, Fire: 199</t>
+        </is>
+      </c>
+      <c r="H68" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="I68" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="J68" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="K68" s="5" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="5" t="n">
+        <v>64</v>
+      </c>
+      <c r="B69" s="5" t="inlineStr">
+        <is>
+          <t>Tunisia</t>
+        </is>
+      </c>
+      <c r="C69" s="5" t="inlineStr">
+        <is>
+          <t>TN</t>
+        </is>
+      </c>
+      <c r="D69" s="5" t="inlineStr">
+        <is>
+          <t>(default)</t>
+        </is>
+      </c>
+      <c r="E69" s="5" t="inlineStr"/>
+      <c r="F69" s="5" t="inlineStr"/>
+      <c r="G69" s="5" t="inlineStr">
+        <is>
+          <t>Police: 197, Ambulance: 190, Fire: 198</t>
+        </is>
+      </c>
+      <c r="H69" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="I69" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="J69" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="K69" s="5" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="5" t="n">
+        <v>65</v>
+      </c>
+      <c r="B70" s="5" t="inlineStr">
+        <is>
+          <t>Turkey</t>
+        </is>
+      </c>
+      <c r="C70" s="5" t="inlineStr">
+        <is>
+          <t>TR</t>
+        </is>
+      </c>
+      <c r="D70" s="5" t="inlineStr">
+        <is>
+          <t>(default)</t>
+        </is>
+      </c>
+      <c r="E70" s="5" t="inlineStr"/>
+      <c r="F70" s="5" t="inlineStr"/>
+      <c r="G70" s="5" t="inlineStr">
+        <is>
+          <t>Police: 112, Ambulance: 112, Fire: 112</t>
+        </is>
+      </c>
+      <c r="H70" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="I70" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="J70" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="K70" s="5" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="5" t="n">
+        <v>66</v>
+      </c>
+      <c r="B71" s="5" t="inlineStr">
+        <is>
+          <t>Tanzania</t>
+        </is>
+      </c>
+      <c r="C71" s="5" t="inlineStr">
+        <is>
+          <t>TZ</t>
+        </is>
+      </c>
+      <c r="D71" s="5" t="inlineStr">
+        <is>
+          <t>(default)</t>
+        </is>
+      </c>
+      <c r="E71" s="5" t="inlineStr"/>
+      <c r="F71" s="5" t="inlineStr"/>
+      <c r="G71" s="5" t="inlineStr">
+        <is>
+          <t>Police: 112, Ambulance: 114, Fire: 115</t>
+        </is>
+      </c>
+      <c r="H71" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="I71" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="J71" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="K71" s="5" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="5" t="n">
+        <v>67</v>
+      </c>
+      <c r="B72" s="5" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
+      <c r="C72" s="5" t="inlineStr">
+        <is>
+          <t>UA</t>
+        </is>
+      </c>
+      <c r="D72" s="5" t="inlineStr">
+        <is>
+          <t>(default)</t>
+        </is>
+      </c>
+      <c r="E72" s="5" t="inlineStr"/>
+      <c r="F72" s="5" t="inlineStr"/>
+      <c r="G72" s="5" t="inlineStr">
+        <is>
+          <t>General Emergency: 112, Police: 102, Ambulance: 103, Fire: 101</t>
+        </is>
+      </c>
+      <c r="H72" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="I72" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="J72" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="K72" s="5" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="5" t="n">
+        <v>68</v>
+      </c>
+      <c r="B73" s="5" t="inlineStr">
+        <is>
+          <t>Uganda</t>
+        </is>
+      </c>
+      <c r="C73" s="5" t="inlineStr">
+        <is>
+          <t>UG</t>
+        </is>
+      </c>
+      <c r="D73" s="5" t="inlineStr">
+        <is>
+          <t>(default)</t>
+        </is>
+      </c>
+      <c r="E73" s="5" t="inlineStr"/>
+      <c r="F73" s="5" t="inlineStr"/>
+      <c r="G73" s="5" t="inlineStr">
+        <is>
+          <t>Police: 112, Ambulance: 911, Fire: 112</t>
+        </is>
+      </c>
+      <c r="H73" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="I73" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="J73" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="K73" s="5" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="5" t="n">
+        <v>69</v>
+      </c>
+      <c r="B74" s="5" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="C74" s="5" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="D74" s="5" t="inlineStr">
+        <is>
+          <t>(default)</t>
+        </is>
+      </c>
+      <c r="E74" s="5" t="inlineStr"/>
+      <c r="F74" s="5" t="inlineStr"/>
+      <c r="G74" s="5" t="inlineStr">
+        <is>
+          <t>General Emergency: 911, Police: 911, Ambulance: 911, Fire: 911, Suicide Helpline: 988</t>
+        </is>
+      </c>
+      <c r="H74" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I74" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J74" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K74" s="5" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="5" t="n">
+        <v>70</v>
+      </c>
+      <c r="B75" s="5" t="inlineStr">
+        <is>
+          <t>Uzbekistan</t>
+        </is>
+      </c>
+      <c r="C75" s="5" t="inlineStr">
+        <is>
+          <t>UZ</t>
+        </is>
+      </c>
+      <c r="D75" s="5" t="inlineStr">
+        <is>
+          <t>(default)</t>
+        </is>
+      </c>
+      <c r="E75" s="5" t="inlineStr"/>
+      <c r="F75" s="5" t="inlineStr"/>
+      <c r="G75" s="5" t="inlineStr">
+        <is>
+          <t>Police: 102, Ambulance: 101, Fire: 103</t>
+        </is>
+      </c>
+      <c r="H75" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="I75" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="J75" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="K75" s="5" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="5" t="n">
+        <v>71</v>
+      </c>
+      <c r="B76" s="5" t="inlineStr">
+        <is>
+          <t>Venezuela</t>
+        </is>
+      </c>
+      <c r="C76" s="5" t="inlineStr">
+        <is>
+          <t>VE</t>
+        </is>
+      </c>
+      <c r="D76" s="5" t="inlineStr">
+        <is>
+          <t>(default)</t>
+        </is>
+      </c>
+      <c r="E76" s="5" t="inlineStr"/>
+      <c r="F76" s="5" t="inlineStr"/>
+      <c r="G76" s="5" t="inlineStr">
+        <is>
+          <t>Police: 911, Ambulance: 911, Fire: 911</t>
+        </is>
+      </c>
+      <c r="H76" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="I76" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="J76" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="K76" s="5" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="5" t="n">
+        <v>72</v>
+      </c>
+      <c r="B77" s="5" t="inlineStr">
+        <is>
+          <t>Vietnam</t>
+        </is>
+      </c>
+      <c r="C77" s="5" t="inlineStr">
+        <is>
+          <t>VN</t>
+        </is>
+      </c>
+      <c r="D77" s="5" t="inlineStr">
+        <is>
+          <t>(default)</t>
+        </is>
+      </c>
+      <c r="E77" s="5" t="inlineStr"/>
+      <c r="F77" s="5" t="inlineStr"/>
+      <c r="G77" s="5" t="inlineStr">
+        <is>
+          <t>Police: 113, Ambulance: 115, Fire: 114</t>
+        </is>
+      </c>
+      <c r="H77" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="I77" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="J77" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="K77" s="5" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="5" t="n">
+        <v>73</v>
+      </c>
+      <c r="B78" s="5" t="inlineStr">
+        <is>
+          <t>South Africa</t>
+        </is>
+      </c>
+      <c r="C78" s="5" t="inlineStr">
+        <is>
+          <t>ZA</t>
+        </is>
+      </c>
+      <c r="D78" s="5" t="inlineStr">
+        <is>
+          <t>(default)</t>
+        </is>
+      </c>
+      <c r="E78" s="5" t="inlineStr"/>
+      <c r="F78" s="5" t="inlineStr"/>
+      <c r="G78" s="5" t="inlineStr">
+        <is>
+          <t>Police: 10 111, Ambulance: 10 177, Fire: 10 177</t>
+        </is>
+      </c>
+      <c r="H78" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="I78" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="J78" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="K78" s="5" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="4" t="inlineStr">
+        <is>
+          <t>SECTION 2: India — State-Level Contacts (all 3 states)</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="5" t="n">
+        <v>74</v>
+      </c>
+      <c r="B80" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C80" s="5" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="D80" s="5" t="inlineStr">
+        <is>
+          <t>Karnataka</t>
+        </is>
+      </c>
+      <c r="E80" s="5" t="inlineStr">
+        <is>
+          <t>KA</t>
+        </is>
+      </c>
+      <c r="F80" s="5" t="inlineStr"/>
+      <c r="G80" s="5" t="inlineStr">
+        <is>
+          <t>Police: 112, Ambulance: 108, Fire: 101</t>
+        </is>
+      </c>
+      <c r="H80" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="I80" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="J80" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="K80" s="5" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="5" t="n">
+        <v>75</v>
+      </c>
+      <c r="B81" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C81" s="5" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="D81" s="5" t="inlineStr">
+        <is>
+          <t>Maharashtra</t>
+        </is>
+      </c>
+      <c r="E81" s="5" t="inlineStr">
+        <is>
+          <t>MH</t>
+        </is>
+      </c>
+      <c r="F81" s="5" t="inlineStr"/>
+      <c r="G81" s="5" t="inlineStr">
+        <is>
+          <t>Police: 112, Ambulance: 108, Fire: 101</t>
+        </is>
+      </c>
+      <c r="H81" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="I81" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="J81" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="K81" s="5" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="5" t="n">
+        <v>76</v>
+      </c>
+      <c r="B82" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C82" s="5" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="D82" s="5" t="inlineStr">
+        <is>
+          <t>Tamil Nadu</t>
+        </is>
+      </c>
+      <c r="E82" s="5" t="inlineStr">
+        <is>
+          <t>TN</t>
+        </is>
+      </c>
+      <c r="F82" s="5" t="inlineStr"/>
+      <c r="G82" s="5" t="inlineStr">
+        <is>
+          <t>Police: 112, Ambulance: 108, Fire: 101</t>
+        </is>
+      </c>
+      <c r="H82" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="I82" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="J82" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="K82" s="5" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="4" t="inlineStr">
+        <is>
+          <t>SECTION 3: India — City-Level Contacts (all cities)</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="5" t="n">
+        <v>77</v>
+      </c>
+      <c r="B84" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C84" s="5" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="D84" s="5" t="inlineStr">
+        <is>
+          <t>Karnataka</t>
+        </is>
+      </c>
+      <c r="E84" s="5" t="inlineStr">
+        <is>
+          <t>KA</t>
+        </is>
+      </c>
+      <c r="F84" s="5" t="inlineStr">
+        <is>
+          <t>Bengaluru</t>
+        </is>
+      </c>
+      <c r="G84" s="5" t="inlineStr">
+        <is>
+          <t>Police: 112, Ambulance: 108</t>
+        </is>
+      </c>
+      <c r="H84" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="I84" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="J84" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="K84" s="5" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="5" t="n">
+        <v>78</v>
+      </c>
+      <c r="B85" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C85" s="5" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="D85" s="5" t="inlineStr">
+        <is>
+          <t>Karnataka</t>
+        </is>
+      </c>
+      <c r="E85" s="5" t="inlineStr">
+        <is>
+          <t>KA</t>
+        </is>
+      </c>
+      <c r="F85" s="5" t="inlineStr">
+        <is>
+          <t>Hubli</t>
+        </is>
+      </c>
+      <c r="G85" s="5" t="inlineStr">
+        <is>
+          <t>Police: 112, Ambulance: 108</t>
+        </is>
+      </c>
+      <c r="H85" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="I85" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="J85" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="K85" s="5" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="5" t="n">
+        <v>79</v>
+      </c>
+      <c r="B86" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C86" s="5" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="D86" s="5" t="inlineStr">
+        <is>
+          <t>Karnataka</t>
+        </is>
+      </c>
+      <c r="E86" s="5" t="inlineStr">
+        <is>
+          <t>KA</t>
+        </is>
+      </c>
+      <c r="F86" s="5" t="inlineStr">
+        <is>
+          <t>Mysuru</t>
+        </is>
+      </c>
+      <c r="G86" s="5" t="inlineStr">
+        <is>
+          <t>Police: 112, Ambulance: 108</t>
+        </is>
+      </c>
+      <c r="H86" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="I86" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="J86" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="K86" s="5" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="5" t="n">
+        <v>80</v>
+      </c>
+      <c r="B87" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C87" s="5" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="D87" s="5" t="inlineStr">
+        <is>
+          <t>Karnataka</t>
+        </is>
+      </c>
+      <c r="E87" s="5" t="inlineStr">
+        <is>
+          <t>KA</t>
+        </is>
+      </c>
+      <c r="F87" s="5" t="inlineStr">
+        <is>
+          <t>Tumakuru</t>
+        </is>
+      </c>
+      <c r="G87" s="5" t="inlineStr">
+        <is>
+          <t>Police: 112, Ambulance: 108</t>
+        </is>
+      </c>
+      <c r="H87" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="I87" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="J87" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="K87" s="5" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="5" t="n">
+        <v>81</v>
+      </c>
+      <c r="B88" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C88" s="5" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="D88" s="5" t="inlineStr">
+        <is>
+          <t>Maharashtra</t>
+        </is>
+      </c>
+      <c r="E88" s="5" t="inlineStr">
+        <is>
+          <t>MH</t>
+        </is>
+      </c>
+      <c r="F88" s="5" t="inlineStr">
+        <is>
+          <t>Mumbai</t>
+        </is>
+      </c>
+      <c r="G88" s="5" t="inlineStr">
+        <is>
+          <t>Police: 112, Ambulance: 108</t>
+        </is>
+      </c>
+      <c r="H88" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="I88" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="J88" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="K88" s="5" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="5" t="n">
+        <v>82</v>
+      </c>
+      <c r="B89" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C89" s="5" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="D89" s="5" t="inlineStr">
+        <is>
+          <t>Maharashtra</t>
+        </is>
+      </c>
+      <c r="E89" s="5" t="inlineStr">
+        <is>
+          <t>MH</t>
+        </is>
+      </c>
+      <c r="F89" s="5" t="inlineStr">
+        <is>
+          <t>Pune</t>
+        </is>
+      </c>
+      <c r="G89" s="5" t="inlineStr">
+        <is>
+          <t>Police: 112, Ambulance: 108</t>
+        </is>
+      </c>
+      <c r="H89" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="I89" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="J89" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="K89" s="5" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="5" t="n">
+        <v>83</v>
+      </c>
+      <c r="B90" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C90" s="5" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="D90" s="5" t="inlineStr">
+        <is>
+          <t>Tamil Nadu</t>
+        </is>
+      </c>
+      <c r="E90" s="5" t="inlineStr">
+        <is>
+          <t>TN</t>
+        </is>
+      </c>
+      <c r="F90" s="5" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+      <c r="G90" s="5" t="inlineStr">
+        <is>
+          <t>Police: 112, Ambulance: 108</t>
+        </is>
+      </c>
+      <c r="H90" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="I90" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="J90" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="K90" s="5" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="4" t="inlineStr">
+        <is>
+          <t>SECTION 4: India — ZIP-Level Contacts (all ZIPs)</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="5" t="n">
+        <v>84</v>
+      </c>
+      <c r="B92" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C92" s="5" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="D92" s="5" t="inlineStr">
+        <is>
+          <t>Karnataka</t>
+        </is>
+      </c>
+      <c r="E92" s="5" t="inlineStr">
+        <is>
+          <t>KA</t>
+        </is>
+      </c>
+      <c r="F92" s="5" t="inlineStr">
+        <is>
+          <t>560001</t>
+        </is>
+      </c>
+      <c r="G92" s="5" t="inlineStr">
+        <is>
+          <t>Police: 112, Ambulance: 108</t>
+        </is>
+      </c>
+      <c r="H92" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="I92" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="J92" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="K92" s="5" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="5" t="n">
+        <v>85</v>
+      </c>
+      <c r="B93" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C93" s="5" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="D93" s="5" t="inlineStr">
+        <is>
+          <t>Karnataka</t>
+        </is>
+      </c>
+      <c r="E93" s="5" t="inlineStr">
+        <is>
+          <t>KA</t>
+        </is>
+      </c>
+      <c r="F93" s="5" t="inlineStr">
+        <is>
+          <t>560002</t>
+        </is>
+      </c>
+      <c r="G93" s="5" t="inlineStr">
+        <is>
+          <t>Police: 112, Ambulance: 108</t>
+        </is>
+      </c>
+      <c r="H93" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="I93" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="J93" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="K93" s="5" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="5" t="n">
+        <v>86</v>
+      </c>
+      <c r="B94" s="5" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="C94" s="5" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="D94" s="5" t="inlineStr">
+        <is>
+          <t>Karnataka</t>
+        </is>
+      </c>
+      <c r="E94" s="5" t="inlineStr">
+        <is>
+          <t>KA</t>
+        </is>
+      </c>
+      <c r="F94" s="5" t="inlineStr">
+        <is>
+          <t>572103</t>
+        </is>
+      </c>
+      <c r="G94" s="5" t="inlineStr">
+        <is>
+          <t>Police: 112, Ambulance: 108</t>
+        </is>
+      </c>
+      <c r="H94" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="I94" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="J94" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="K94" s="5" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="4" t="inlineStr">
+        <is>
+          <t>SECTION 5: US — State-Level Contacts (all 50 states + Puerto Rico)</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="5" t="n">
+        <v>87</v>
+      </c>
+      <c r="B96" s="5" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="C96" s="5" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="D96" s="5" t="inlineStr">
+        <is>
+          <t>Alabama</t>
+        </is>
+      </c>
+      <c r="E96" s="5" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="F96" s="5" t="inlineStr"/>
+      <c r="G96" s="5" t="inlineStr">
+        <is>
+          <t>Police: 911, Ambulance: 911, Fire: 911, Suicide Helpline: 988</t>
+        </is>
+      </c>
+      <c r="H96" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="I96" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="J96" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="K96" s="5" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="5" t="n">
+        <v>88</v>
+      </c>
+      <c r="B97" s="5" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="C97" s="5" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="D97" s="5" t="inlineStr">
+        <is>
+          <t>Alaska</t>
+        </is>
+      </c>
+      <c r="E97" s="5" t="inlineStr">
+        <is>
+          <t>AK</t>
+        </is>
+      </c>
+      <c r="F97" s="5" t="inlineStr"/>
+      <c r="G97" s="5" t="inlineStr">
+        <is>
+          <t>Police: 911, Ambulance: 911, Fire: 911, Suicide Helpline: 988</t>
+        </is>
+      </c>
+      <c r="H97" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="I97" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="J97" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="K97" s="5" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="5" t="n">
+        <v>89</v>
+      </c>
+      <c r="B98" s="5" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="C98" s="5" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="D98" s="5" t="inlineStr">
+        <is>
+          <t>Arizona</t>
+        </is>
+      </c>
+      <c r="E98" s="5" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="F98" s="5" t="inlineStr"/>
+      <c r="G98" s="5" t="inlineStr">
+        <is>
+          <t>Police: 911, Ambulance: 911, Fire: 911, Suicide Helpline: 988</t>
+        </is>
+      </c>
+      <c r="H98" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="I98" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="J98" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="K98" s="5" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="5" t="n">
+        <v>90</v>
+      </c>
+      <c r="B99" s="5" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="C99" s="5" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="D99" s="5" t="inlineStr">
+        <is>
+          <t>Arkansas</t>
+        </is>
+      </c>
+      <c r="E99" s="5" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="F99" s="5" t="inlineStr"/>
+      <c r="G99" s="5" t="inlineStr">
+        <is>
+          <t>Police: 911, Ambulance: 911, Fire: 911, Suicide Helpline: 988</t>
+        </is>
+      </c>
+      <c r="H99" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="I99" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="J99" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="K99" s="5" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="5" t="n">
+        <v>91</v>
+      </c>
+      <c r="B100" s="5" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="C100" s="5" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="D100" s="5" t="inlineStr">
+        <is>
+          <t>California</t>
+        </is>
+      </c>
+      <c r="E100" s="5" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="F100" s="5" t="inlineStr"/>
+      <c r="G100" s="5" t="inlineStr">
+        <is>
+          <t>Police: 911, Ambulance: 911, Fire: 911, Suicide Helpline: 988</t>
+        </is>
+      </c>
+      <c r="H100" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I100" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J100" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K100" s="5" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" s="5" t="n">
+        <v>92</v>
+      </c>
+      <c r="B101" s="5" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="C101" s="5" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="D101" s="5" t="inlineStr">
+        <is>
+          <t>Colorado</t>
+        </is>
+      </c>
+      <c r="E101" s="5" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+      <c r="F101" s="5" t="inlineStr"/>
+      <c r="G101" s="5" t="inlineStr">
+        <is>
+          <t>Police: 911, Ambulance: 911, Fire: 911, Suicide Helpline: 988</t>
+        </is>
+      </c>
+      <c r="H101" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="I101" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="J101" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="K101" s="5" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" s="5" t="n">
+        <v>93</v>
+      </c>
+      <c r="B102" s="5" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="C102" s="5" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="D102" s="5" t="inlineStr">
+        <is>
+          <t>Connecticut</t>
+        </is>
+      </c>
+      <c r="E102" s="5" t="inlineStr">
+        <is>
+          <t>CT</t>
+        </is>
+      </c>
+      <c r="F102" s="5" t="inlineStr"/>
+      <c r="G102" s="5" t="inlineStr">
+        <is>
+          <t>Police: 911, Ambulance: 911, Fire: 911, Suicide Helpline: 988</t>
+        </is>
+      </c>
+      <c r="H102" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="I102" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="J102" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="K102" s="5" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" s="5" t="n">
+        <v>94</v>
+      </c>
+      <c r="B103" s="5" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="C103" s="5" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="D103" s="5" t="inlineStr">
+        <is>
+          <t>Delaware</t>
+        </is>
+      </c>
+      <c r="E103" s="5" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="F103" s="5" t="inlineStr"/>
+      <c r="G103" s="5" t="inlineStr">
+        <is>
+          <t>Police: 911, Ambulance: 911, Fire: 911, Suicide Helpline: 988</t>
+        </is>
+      </c>
+      <c r="H103" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="I103" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="J103" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="K103" s="5" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" s="5" t="n">
+        <v>95</v>
+      </c>
+      <c r="B104" s="5" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="C104" s="5" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="D104" s="5" t="inlineStr">
+        <is>
+          <t>Florida</t>
+        </is>
+      </c>
+      <c r="E104" s="5" t="inlineStr">
+        <is>
+          <t>FL</t>
+        </is>
+      </c>
+      <c r="F104" s="5" t="inlineStr"/>
+      <c r="G104" s="5" t="inlineStr">
+        <is>
+          <t>Police: 911, Ambulance: 911, Fire: 911, Suicide Helpline: 988</t>
+        </is>
+      </c>
+      <c r="H104" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="I104" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="J104" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="K104" s="5" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" s="5" t="n">
+        <v>96</v>
+      </c>
+      <c r="B105" s="5" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="C105" s="5" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="D105" s="5" t="inlineStr">
+        <is>
+          <t>Georgia</t>
+        </is>
+      </c>
+      <c r="E105" s="5" t="inlineStr">
+        <is>
+          <t>GA</t>
+        </is>
+      </c>
+      <c r="F105" s="5" t="inlineStr"/>
+      <c r="G105" s="5" t="inlineStr">
+        <is>
+          <t>Should fall back to US default: General Emergency: 911, Police: 911, Ambulance: 911, Fire: 911, Suicide Helpline: 988</t>
+        </is>
+      </c>
+      <c r="H105" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="I105" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="J105" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="K105" s="5" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" s="5" t="n">
+        <v>97</v>
+      </c>
+      <c r="B106" s="5" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="C106" s="5" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="D106" s="5" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="E106" s="5" t="inlineStr">
+        <is>
+          <t>HI</t>
+        </is>
+      </c>
+      <c r="F106" s="5" t="inlineStr"/>
+      <c r="G106" s="5" t="inlineStr">
+        <is>
+          <t>Police: 911, Ambulance: 911, Fire: 911, Suicide Helpline: 988</t>
+        </is>
+      </c>
+      <c r="H106" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="I106" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="J106" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="K106" s="5" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" s="5" t="n">
+        <v>98</v>
+      </c>
+      <c r="B107" s="5" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="C107" s="5" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="D107" s="5" t="inlineStr">
+        <is>
+          <t>Idaho</t>
+        </is>
+      </c>
+      <c r="E107" s="5" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="F107" s="5" t="inlineStr"/>
+      <c r="G107" s="5" t="inlineStr">
+        <is>
+          <t>Police: 911, Ambulance: 911, Fire: 911, Suicide Helpline: 988</t>
+        </is>
+      </c>
+      <c r="H107" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="I107" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="J107" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="K107" s="5" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" s="5" t="n">
+        <v>99</v>
+      </c>
+      <c r="B108" s="5" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="C108" s="5" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="D108" s="5" t="inlineStr">
+        <is>
+          <t>Illinois</t>
+        </is>
+      </c>
+      <c r="E108" s="5" t="inlineStr">
+        <is>
+          <t>IL</t>
+        </is>
+      </c>
+      <c r="F108" s="5" t="inlineStr"/>
+      <c r="G108" s="5" t="inlineStr">
+        <is>
+          <t>Police: 911, Ambulance: 911, Fire: 911, Suicide Helpline: 988</t>
+        </is>
+      </c>
+      <c r="H108" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="I108" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="J108" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="K108" s="5" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="B109" s="5" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="C109" s="5" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="D109" s="5" t="inlineStr">
+        <is>
+          <t>Indiana</t>
+        </is>
+      </c>
+      <c r="E109" s="5" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="F109" s="5" t="inlineStr"/>
+      <c r="G109" s="5" t="inlineStr">
+        <is>
+          <t>Police: 911, Ambulance: 911, Fire: 911, Suicide Helpline: 988</t>
+        </is>
+      </c>
+      <c r="H109" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="I109" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="J109" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="K109" s="5" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" s="5" t="n">
+        <v>101</v>
+      </c>
+      <c r="B110" s="5" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="C110" s="5" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="D110" s="5" t="inlineStr">
+        <is>
+          <t>Iowa</t>
+        </is>
+      </c>
+      <c r="E110" s="5" t="inlineStr">
+        <is>
+          <t>IA</t>
+        </is>
+      </c>
+      <c r="F110" s="5" t="inlineStr"/>
+      <c r="G110" s="5" t="inlineStr">
+        <is>
+          <t>Police: 911, Ambulance: 911, Fire: 911, Suicide Helpline: 988</t>
+        </is>
+      </c>
+      <c r="H110" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="I110" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="J110" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="K110" s="5" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" s="5" t="n">
+        <v>102</v>
+      </c>
+      <c r="B111" s="5" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="C111" s="5" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="D111" s="5" t="inlineStr">
+        <is>
+          <t>Kansas</t>
+        </is>
+      </c>
+      <c r="E111" s="5" t="inlineStr">
+        <is>
+          <t>KS</t>
+        </is>
+      </c>
+      <c r="F111" s="5" t="inlineStr"/>
+      <c r="G111" s="5" t="inlineStr">
+        <is>
+          <t>Police: 911, Ambulance: 911, Fire: 911, Suicide Helpline: 988</t>
+        </is>
+      </c>
+      <c r="H111" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="I111" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="J111" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="K111" s="5" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" s="5" t="n">
+        <v>103</v>
+      </c>
+      <c r="B112" s="5" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="C112" s="5" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="D112" s="5" t="inlineStr">
+        <is>
+          <t>Kentucky</t>
+        </is>
+      </c>
+      <c r="E112" s="5" t="inlineStr">
+        <is>
+          <t>KY</t>
+        </is>
+      </c>
+      <c r="F112" s="5" t="inlineStr"/>
+      <c r="G112" s="5" t="inlineStr">
+        <is>
+          <t>Police: 911, Ambulance: 911, Fire: 911, Suicide Helpline: 988</t>
+        </is>
+      </c>
+      <c r="H112" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="I112" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="J112" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="K112" s="5" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" s="5" t="n">
+        <v>104</v>
+      </c>
+      <c r="B113" s="5" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="C113" s="5" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="D113" s="5" t="inlineStr">
+        <is>
+          <t>Louisiana</t>
+        </is>
+      </c>
+      <c r="E113" s="5" t="inlineStr">
+        <is>
+          <t>LA</t>
+        </is>
+      </c>
+      <c r="F113" s="5" t="inlineStr"/>
+      <c r="G113" s="5" t="inlineStr">
+        <is>
+          <t>Police: 911, Ambulance: 911, Fire: 911, Suicide Helpline: 988</t>
+        </is>
+      </c>
+      <c r="H113" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="I113" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="J113" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="K113" s="5" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" s="5" t="n">
+        <v>105</v>
+      </c>
+      <c r="B114" s="5" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="C114" s="5" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="D114" s="5" t="inlineStr">
+        <is>
+          <t>Maine</t>
+        </is>
+      </c>
+      <c r="E114" s="5" t="inlineStr">
+        <is>
+          <t>ME</t>
+        </is>
+      </c>
+      <c r="F114" s="5" t="inlineStr"/>
+      <c r="G114" s="5" t="inlineStr">
+        <is>
+          <t>Police: 911, Ambulance: 911, Fire: 911, Suicide Helpline: 988</t>
+        </is>
+      </c>
+      <c r="H114" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="I114" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="J114" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="K114" s="5" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" s="5" t="n">
+        <v>106</v>
+      </c>
+      <c r="B115" s="5" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="C115" s="5" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="D115" s="5" t="inlineStr">
+        <is>
+          <t>Maryland</t>
+        </is>
+      </c>
+      <c r="E115" s="5" t="inlineStr">
+        <is>
+          <t>MD</t>
+        </is>
+      </c>
+      <c r="F115" s="5" t="inlineStr"/>
+      <c r="G115" s="5" t="inlineStr">
+        <is>
+          <t>Police: 911, Ambulance: 911, Fire: 911, Suicide Helpline: 988</t>
+        </is>
+      </c>
+      <c r="H115" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="I115" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="J115" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="K115" s="5" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" s="5" t="n">
+        <v>107</v>
+      </c>
+      <c r="B116" s="5" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="C116" s="5" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="D116" s="5" t="inlineStr">
+        <is>
+          <t>Massachusetts</t>
+        </is>
+      </c>
+      <c r="E116" s="5" t="inlineStr">
+        <is>
+          <t>MA</t>
+        </is>
+      </c>
+      <c r="F116" s="5" t="inlineStr"/>
+      <c r="G116" s="5" t="inlineStr">
+        <is>
+          <t>Police: 911, Ambulance: 911, Fire: 911, Suicide Helpline: 988</t>
+        </is>
+      </c>
+      <c r="H116" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="I116" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="J116" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="K116" s="5" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" s="5" t="n">
+        <v>108</v>
+      </c>
+      <c r="B117" s="5" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="C117" s="5" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="D117" s="5" t="inlineStr">
+        <is>
+          <t>Michigan</t>
+        </is>
+      </c>
+      <c r="E117" s="5" t="inlineStr">
+        <is>
+          <t>MI</t>
+        </is>
+      </c>
+      <c r="F117" s="5" t="inlineStr"/>
+      <c r="G117" s="5" t="inlineStr">
+        <is>
+          <t>Police: 911, Ambulance: 911, Fire: 911, Suicide Helpline: 988</t>
+        </is>
+      </c>
+      <c r="H117" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="I117" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="J117" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="K117" s="5" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" s="5" t="n">
+        <v>109</v>
+      </c>
+      <c r="B118" s="5" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="C118" s="5" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="D118" s="5" t="inlineStr">
+        <is>
+          <t>Minnesota</t>
+        </is>
+      </c>
+      <c r="E118" s="5" t="inlineStr">
+        <is>
+          <t>MN</t>
+        </is>
+      </c>
+      <c r="F118" s="5" t="inlineStr"/>
+      <c r="G118" s="5" t="inlineStr">
+        <is>
+          <t>Police: 911, Ambulance: 911, Fire: 911, Suicide Helpline: 988</t>
+        </is>
+      </c>
+      <c r="H118" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="I118" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="J118" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="K118" s="5" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" s="5" t="n">
+        <v>110</v>
+      </c>
+      <c r="B119" s="5" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="C119" s="5" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="D119" s="5" t="inlineStr">
+        <is>
+          <t>Mississippi</t>
+        </is>
+      </c>
+      <c r="E119" s="5" t="inlineStr">
+        <is>
+          <t>MS</t>
+        </is>
+      </c>
+      <c r="F119" s="5" t="inlineStr"/>
+      <c r="G119" s="5" t="inlineStr">
+        <is>
+          <t>Police: 911, Ambulance: 911, Fire: 911, Suicide Helpline: 988</t>
+        </is>
+      </c>
+      <c r="H119" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="I119" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="J119" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="K119" s="5" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" s="5" t="n">
+        <v>111</v>
+      </c>
+      <c r="B120" s="5" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="C120" s="5" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="D120" s="5" t="inlineStr">
+        <is>
+          <t>Missouri</t>
+        </is>
+      </c>
+      <c r="E120" s="5" t="inlineStr">
+        <is>
+          <t>MO</t>
+        </is>
+      </c>
+      <c r="F120" s="5" t="inlineStr"/>
+      <c r="G120" s="5" t="inlineStr">
+        <is>
+          <t>Police: 911, Ambulance: 911, Fire: 911, Suicide Helpline: 988</t>
+        </is>
+      </c>
+      <c r="H120" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="I120" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="J120" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="K120" s="5" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" s="5" t="n">
+        <v>112</v>
+      </c>
+      <c r="B121" s="5" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="C121" s="5" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="D121" s="5" t="inlineStr">
+        <is>
+          <t>Montana</t>
+        </is>
+      </c>
+      <c r="E121" s="5" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+      <c r="F121" s="5" t="inlineStr"/>
+      <c r="G121" s="5" t="inlineStr">
+        <is>
+          <t>Police: 911, Ambulance: 911, Fire: 911, Suicide Helpline: 988</t>
+        </is>
+      </c>
+      <c r="H121" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="I121" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="J121" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="K121" s="5" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" s="5" t="n">
+        <v>113</v>
+      </c>
+      <c r="B122" s="5" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="C122" s="5" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="D122" s="5" t="inlineStr">
+        <is>
+          <t>Nebraska</t>
+        </is>
+      </c>
+      <c r="E122" s="5" t="inlineStr">
+        <is>
+          <t>NE</t>
+        </is>
+      </c>
+      <c r="F122" s="5" t="inlineStr"/>
+      <c r="G122" s="5" t="inlineStr">
+        <is>
+          <t>Police: 911, Ambulance: 911, Fire: 911, Suicide Helpline: 988</t>
+        </is>
+      </c>
+      <c r="H122" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="I122" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="J122" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="K122" s="5" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" s="5" t="n">
+        <v>114</v>
+      </c>
+      <c r="B123" s="5" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="C123" s="5" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="D123" s="5" t="inlineStr">
+        <is>
+          <t>Nevada</t>
+        </is>
+      </c>
+      <c r="E123" s="5" t="inlineStr">
+        <is>
+          <t>NV</t>
+        </is>
+      </c>
+      <c r="F123" s="5" t="inlineStr"/>
+      <c r="G123" s="5" t="inlineStr">
+        <is>
+          <t>Police: 911, Ambulance: 911, Fire: 911, Suicide Helpline: 988</t>
+        </is>
+      </c>
+      <c r="H123" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="I123" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="J123" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="K123" s="5" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" s="5" t="n">
+        <v>115</v>
+      </c>
+      <c r="B124" s="5" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="C124" s="5" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="D124" s="5" t="inlineStr">
+        <is>
+          <t>New Hampshire</t>
+        </is>
+      </c>
+      <c r="E124" s="5" t="inlineStr">
+        <is>
+          <t>NH</t>
+        </is>
+      </c>
+      <c r="F124" s="5" t="inlineStr"/>
+      <c r="G124" s="5" t="inlineStr">
+        <is>
+          <t>Police: 911, Ambulance: 911, Fire: 911, Suicide Helpline: 988</t>
+        </is>
+      </c>
+      <c r="H124" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="I124" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="J124" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="K124" s="5" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" s="5" t="n">
+        <v>116</v>
+      </c>
+      <c r="B125" s="5" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="C125" s="5" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="D125" s="5" t="inlineStr">
+        <is>
+          <t>New Jersey</t>
+        </is>
+      </c>
+      <c r="E125" s="5" t="inlineStr">
+        <is>
+          <t>NJ</t>
+        </is>
+      </c>
+      <c r="F125" s="5" t="inlineStr"/>
+      <c r="G125" s="5" t="inlineStr">
+        <is>
+          <t>Police: 911, Ambulance: 911, Fire: 911, Suicide Helpline: 988</t>
+        </is>
+      </c>
+      <c r="H125" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="I125" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="J125" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="K125" s="5" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" s="5" t="n">
+        <v>117</v>
+      </c>
+      <c r="B126" s="5" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="C126" s="5" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="D126" s="5" t="inlineStr">
+        <is>
+          <t>New Mexico</t>
+        </is>
+      </c>
+      <c r="E126" s="5" t="inlineStr">
+        <is>
+          <t>NM</t>
+        </is>
+      </c>
+      <c r="F126" s="5" t="inlineStr"/>
+      <c r="G126" s="5" t="inlineStr">
+        <is>
+          <t>Police: 911, Ambulance: 911, Fire: 911, Suicide Helpline: 988</t>
+        </is>
+      </c>
+      <c r="H126" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="I126" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="J126" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="K126" s="5" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" s="5" t="n">
+        <v>118</v>
+      </c>
+      <c r="B127" s="5" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="C127" s="5" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="D127" s="5" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="E127" s="5" t="inlineStr">
+        <is>
+          <t>NY</t>
+        </is>
+      </c>
+      <c r="F127" s="5" t="inlineStr"/>
+      <c r="G127" s="5" t="inlineStr">
+        <is>
+          <t>Police: 911, Ambulance: 911, Fire: 911, Suicide Helpline: 988</t>
+        </is>
+      </c>
+      <c r="H127" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="I127" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="J127" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="K127" s="5" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="A128" s="5" t="n">
+        <v>119</v>
+      </c>
+      <c r="B128" s="5" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="C128" s="5" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="D128" s="5" t="inlineStr">
+        <is>
+          <t>North Carolina</t>
+        </is>
+      </c>
+      <c r="E128" s="5" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="F128" s="5" t="inlineStr"/>
+      <c r="G128" s="5" t="inlineStr">
+        <is>
+          <t>Police: 911, Ambulance: 911, Fire: 911, Suicide Helpline: 988</t>
+        </is>
+      </c>
+      <c r="H128" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="I128" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="J128" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="K128" s="5" t="inlineStr"/>
+    </row>
+    <row r="129">
+      <c r="A129" s="5" t="n">
+        <v>120</v>
+      </c>
+      <c r="B129" s="5" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="C129" s="5" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="D129" s="5" t="inlineStr">
+        <is>
+          <t>North Dakota</t>
+        </is>
+      </c>
+      <c r="E129" s="5" t="inlineStr">
+        <is>
+          <t>ND</t>
+        </is>
+      </c>
+      <c r="F129" s="5" t="inlineStr"/>
+      <c r="G129" s="5" t="inlineStr">
+        <is>
+          <t>Police: 911, Ambulance: 911, Fire: 911, Suicide Helpline: 988</t>
+        </is>
+      </c>
+      <c r="H129" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="I129" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="J129" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="K129" s="5" t="inlineStr"/>
+    </row>
+    <row r="130">
+      <c r="A130" s="5" t="n">
+        <v>121</v>
+      </c>
+      <c r="B130" s="5" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="C130" s="5" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="D130" s="5" t="inlineStr">
+        <is>
+          <t>Ohio</t>
+        </is>
+      </c>
+      <c r="E130" s="5" t="inlineStr">
+        <is>
+          <t>OH</t>
+        </is>
+      </c>
+      <c r="F130" s="5" t="inlineStr"/>
+      <c r="G130" s="5" t="inlineStr">
+        <is>
+          <t>Police: 911, Ambulance: 911, Fire: 911, Suicide Helpline: 988</t>
+        </is>
+      </c>
+      <c r="H130" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="I130" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="J130" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="K130" s="5" t="inlineStr"/>
+    </row>
+    <row r="131">
+      <c r="A131" s="5" t="n">
+        <v>122</v>
+      </c>
+      <c r="B131" s="5" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="C131" s="5" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="D131" s="5" t="inlineStr">
+        <is>
+          <t>Oklahoma</t>
+        </is>
+      </c>
+      <c r="E131" s="5" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F131" s="5" t="inlineStr"/>
+      <c r="G131" s="5" t="inlineStr">
+        <is>
+          <t>Police: 911, Ambulance: 911, Fire: 911, Suicide Helpline: 988</t>
+        </is>
+      </c>
+      <c r="H131" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="I131" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="J131" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="K131" s="5" t="inlineStr"/>
+    </row>
+    <row r="132">
+      <c r="A132" s="5" t="n">
+        <v>123</v>
+      </c>
+      <c r="B132" s="5" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="C132" s="5" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="D132" s="5" t="inlineStr">
+        <is>
+          <t>Oregon</t>
+        </is>
+      </c>
+      <c r="E132" s="5" t="inlineStr">
+        <is>
+          <t>OR</t>
+        </is>
+      </c>
+      <c r="F132" s="5" t="inlineStr"/>
+      <c r="G132" s="5" t="inlineStr">
+        <is>
+          <t>Police: 911, Ambulance: 911, Fire: 911, Suicide Helpline: 988</t>
+        </is>
+      </c>
+      <c r="H132" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="I132" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="J132" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="K132" s="5" t="inlineStr"/>
+    </row>
+    <row r="133">
+      <c r="A133" s="5" t="n">
+        <v>124</v>
+      </c>
+      <c r="B133" s="5" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="C133" s="5" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="D133" s="5" t="inlineStr">
+        <is>
+          <t>Pennsylvania</t>
+        </is>
+      </c>
+      <c r="E133" s="5" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="F133" s="5" t="inlineStr"/>
+      <c r="G133" s="5" t="inlineStr">
+        <is>
+          <t>Police: 911, Ambulance: 911, Fire: 911, Suicide Helpline: 988</t>
+        </is>
+      </c>
+      <c r="H133" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="I133" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="J133" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="K133" s="5" t="inlineStr"/>
+    </row>
+    <row r="134">
+      <c r="A134" s="5" t="n">
+        <v>125</v>
+      </c>
+      <c r="B134" s="5" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="C134" s="5" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="D134" s="5" t="inlineStr">
+        <is>
+          <t>Puerto Rico</t>
+        </is>
+      </c>
+      <c r="E134" s="5" t="inlineStr">
+        <is>
+          <t>PR</t>
+        </is>
+      </c>
+      <c r="F134" s="5" t="inlineStr"/>
+      <c r="G134" s="5" t="inlineStr">
+        <is>
+          <t>Police: 911, Ambulance: 911, Fire: 911, Suicide Helpline: 988</t>
+        </is>
+      </c>
+      <c r="H134" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="I134" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="J134" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="K134" s="5" t="inlineStr"/>
+    </row>
+    <row r="135">
+      <c r="A135" s="5" t="n">
+        <v>126</v>
+      </c>
+      <c r="B135" s="5" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="C135" s="5" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="D135" s="5" t="inlineStr">
+        <is>
+          <t>Rhode Island</t>
+        </is>
+      </c>
+      <c r="E135" s="5" t="inlineStr">
+        <is>
+          <t>RI</t>
+        </is>
+      </c>
+      <c r="F135" s="5" t="inlineStr"/>
+      <c r="G135" s="5" t="inlineStr">
+        <is>
+          <t>Police: 911, Ambulance: 911, Fire: 911, Suicide Helpline: 988</t>
+        </is>
+      </c>
+      <c r="H135" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="I135" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="J135" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="K135" s="5" t="inlineStr"/>
+    </row>
+    <row r="136">
+      <c r="A136" s="5" t="n">
+        <v>127</v>
+      </c>
+      <c r="B136" s="5" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="C136" s="5" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="D136" s="5" t="inlineStr">
+        <is>
+          <t>South Carolina</t>
+        </is>
+      </c>
+      <c r="E136" s="5" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="F136" s="5" t="inlineStr"/>
+      <c r="G136" s="5" t="inlineStr">
+        <is>
+          <t>Police: 911, Ambulance: 911, Fire: 911, Suicide Helpline: 988</t>
+        </is>
+      </c>
+      <c r="H136" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="I136" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="J136" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="K136" s="5" t="inlineStr"/>
+    </row>
+    <row r="137">
+      <c r="A137" s="5" t="n">
+        <v>128</v>
+      </c>
+      <c r="B137" s="5" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="C137" s="5" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="D137" s="5" t="inlineStr">
+        <is>
+          <t>South Dakota</t>
+        </is>
+      </c>
+      <c r="E137" s="5" t="inlineStr">
+        <is>
+          <t>SD</t>
+        </is>
+      </c>
+      <c r="F137" s="5" t="inlineStr"/>
+      <c r="G137" s="5" t="inlineStr">
+        <is>
+          <t>Police: 911, Ambulance: 911, Fire: 911, Suicide Helpline: 988</t>
+        </is>
+      </c>
+      <c r="H137" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="I137" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="J137" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="K137" s="5" t="inlineStr"/>
+    </row>
+    <row r="138">
+      <c r="A138" s="5" t="n">
+        <v>129</v>
+      </c>
+      <c r="B138" s="5" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="C138" s="5" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="D138" s="5" t="inlineStr">
+        <is>
+          <t>Tennessee</t>
+        </is>
+      </c>
+      <c r="E138" s="5" t="inlineStr">
+        <is>
+          <t>TN</t>
+        </is>
+      </c>
+      <c r="F138" s="5" t="inlineStr"/>
+      <c r="G138" s="5" t="inlineStr">
+        <is>
+          <t>Police: 911, Ambulance: 911, Fire: 911, Suicide Helpline: 988</t>
+        </is>
+      </c>
+      <c r="H138" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="I138" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="J138" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="K138" s="5" t="inlineStr"/>
+    </row>
+    <row r="139">
+      <c r="A139" s="5" t="n">
+        <v>130</v>
+      </c>
+      <c r="B139" s="5" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="C139" s="5" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="D139" s="5" t="inlineStr">
+        <is>
+          <t>Texas</t>
+        </is>
+      </c>
+      <c r="E139" s="5" t="inlineStr">
+        <is>
+          <t>TX</t>
+        </is>
+      </c>
+      <c r="F139" s="5" t="inlineStr"/>
+      <c r="G139" s="5" t="inlineStr">
+        <is>
+          <t>Police: 911, Ambulance: 911, Fire: 911, Suicide Helpline: 988</t>
+        </is>
+      </c>
+      <c r="H139" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="I139" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="J139" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="K139" s="5" t="inlineStr"/>
+    </row>
+    <row r="140">
+      <c r="A140" s="5" t="n">
+        <v>131</v>
+      </c>
+      <c r="B140" s="5" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="C140" s="5" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="D140" s="5" t="inlineStr">
+        <is>
+          <t>Utah</t>
+        </is>
+      </c>
+      <c r="E140" s="5" t="inlineStr">
+        <is>
+          <t>UT</t>
+        </is>
+      </c>
+      <c r="F140" s="5" t="inlineStr"/>
+      <c r="G140" s="5" t="inlineStr">
+        <is>
+          <t>Police: 911, Ambulance: 911, Fire: 911, Suicide Helpline: 988</t>
+        </is>
+      </c>
+      <c r="H140" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="I140" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="J140" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="K140" s="5" t="inlineStr"/>
+    </row>
+    <row r="141">
+      <c r="A141" s="5" t="n">
+        <v>132</v>
+      </c>
+      <c r="B141" s="5" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="C141" s="5" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="D141" s="5" t="inlineStr">
+        <is>
+          <t>Vermont</t>
+        </is>
+      </c>
+      <c r="E141" s="5" t="inlineStr">
+        <is>
+          <t>VT</t>
+        </is>
+      </c>
+      <c r="F141" s="5" t="inlineStr"/>
+      <c r="G141" s="5" t="inlineStr">
+        <is>
+          <t>Police: 911, Ambulance: 911, Fire: 911, Suicide Helpline: 988</t>
+        </is>
+      </c>
+      <c r="H141" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="I141" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="J141" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="K141" s="5" t="inlineStr"/>
+    </row>
+    <row r="142">
+      <c r="A142" s="5" t="n">
+        <v>133</v>
+      </c>
+      <c r="B142" s="5" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="C142" s="5" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="D142" s="5" t="inlineStr">
+        <is>
+          <t>Virginia</t>
+        </is>
+      </c>
+      <c r="E142" s="5" t="inlineStr">
+        <is>
+          <t>VA</t>
+        </is>
+      </c>
+      <c r="F142" s="5" t="inlineStr"/>
+      <c r="G142" s="5" t="inlineStr">
+        <is>
+          <t>Police: 911, Ambulance: 911, Fire: 911, Suicide Helpline: 988</t>
+        </is>
+      </c>
+      <c r="H142" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="I142" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="J142" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="K142" s="5" t="inlineStr"/>
+    </row>
+    <row r="143">
+      <c r="A143" s="5" t="n">
+        <v>134</v>
+      </c>
+      <c r="B143" s="5" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="C143" s="5" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="D143" s="5" t="inlineStr">
+        <is>
+          <t>Washington</t>
+        </is>
+      </c>
+      <c r="E143" s="5" t="inlineStr">
+        <is>
+          <t>WA</t>
+        </is>
+      </c>
+      <c r="F143" s="5" t="inlineStr"/>
+      <c r="G143" s="5" t="inlineStr">
+        <is>
+          <t>Police: 911, Ambulance: 911, Fire: 911, Suicide Helpline: 988</t>
+        </is>
+      </c>
+      <c r="H143" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="I143" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="J143" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="K143" s="5" t="inlineStr"/>
+    </row>
+    <row r="144">
+      <c r="A144" s="5" t="n">
+        <v>135</v>
+      </c>
+      <c r="B144" s="5" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="C144" s="5" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="D144" s="5" t="inlineStr">
+        <is>
+          <t>West Virginia</t>
+        </is>
+      </c>
+      <c r="E144" s="5" t="inlineStr">
+        <is>
+          <t>WV</t>
+        </is>
+      </c>
+      <c r="F144" s="5" t="inlineStr"/>
+      <c r="G144" s="5" t="inlineStr">
+        <is>
+          <t>Police: 911, Ambulance: 911, Fire: 911, Suicide Helpline: 988</t>
+        </is>
+      </c>
+      <c r="H144" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="I144" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="J144" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="K144" s="5" t="inlineStr"/>
+    </row>
+    <row r="145">
+      <c r="A145" s="5" t="n">
+        <v>136</v>
+      </c>
+      <c r="B145" s="5" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="C145" s="5" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="D145" s="5" t="inlineStr">
+        <is>
+          <t>Wisconsin</t>
+        </is>
+      </c>
+      <c r="E145" s="5" t="inlineStr">
+        <is>
+          <t>WI</t>
+        </is>
+      </c>
+      <c r="F145" s="5" t="inlineStr"/>
+      <c r="G145" s="5" t="inlineStr">
+        <is>
+          <t>Police: 911, Ambulance: 911, Fire: 911, Suicide Helpline: 988</t>
+        </is>
+      </c>
+      <c r="H145" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="I145" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="J145" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="K145" s="5" t="inlineStr"/>
+    </row>
+    <row r="146">
+      <c r="A146" s="5" t="n">
+        <v>137</v>
+      </c>
+      <c r="B146" s="5" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="C146" s="5" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="D146" s="5" t="inlineStr">
+        <is>
+          <t>Wyoming</t>
+        </is>
+      </c>
+      <c r="E146" s="5" t="inlineStr">
+        <is>
+          <t>WY</t>
+        </is>
+      </c>
+      <c r="F146" s="5" t="inlineStr"/>
+      <c r="G146" s="5" t="inlineStr">
+        <is>
+          <t>Police: 911, Ambulance: 911, Fire: 911, Suicide Helpline: 988</t>
+        </is>
+      </c>
+      <c r="H146" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="I146" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="J146" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="K146" s="5" t="inlineStr"/>
+    </row>
+    <row r="147">
+      <c r="A147" s="4" t="inlineStr">
+        <is>
+          <t>SECTION 6: US — City-Level Contacts (all cities)</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="5" t="n">
+        <v>138</v>
+      </c>
+      <c r="B148" s="5" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="C148" s="5" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="D148" s="5" t="inlineStr">
+        <is>
+          <t>California</t>
+        </is>
+      </c>
+      <c r="E148" s="5" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="F148" s="5" t="inlineStr">
+        <is>
+          <t>Los Angeles</t>
+        </is>
+      </c>
+      <c r="G148" s="5" t="inlineStr">
+        <is>
+          <t>Police: 911, Ambulance: 911, Fire: 911</t>
+        </is>
+      </c>
+      <c r="H148" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="I148" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="J148" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="K148" s="5" t="inlineStr"/>
+    </row>
+    <row r="149">
+      <c r="A149" s="5" t="n">
+        <v>139</v>
+      </c>
+      <c r="B149" s="5" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="C149" s="5" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="D149" s="5" t="inlineStr">
+        <is>
+          <t>California</t>
+        </is>
+      </c>
+      <c r="E149" s="5" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="F149" s="5" t="inlineStr">
+        <is>
+          <t>San Diego</t>
+        </is>
+      </c>
+      <c r="G149" s="5" t="inlineStr">
+        <is>
+          <t>Police: 911, Ambulance: 911, Fire: 911</t>
+        </is>
+      </c>
+      <c r="H149" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="I149" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="J149" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="K149" s="5" t="inlineStr"/>
+    </row>
+    <row r="150">
+      <c r="A150" s="5" t="n">
+        <v>140</v>
+      </c>
+      <c r="B150" s="5" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="C150" s="5" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="D150" s="5" t="inlineStr">
+        <is>
+          <t>California</t>
+        </is>
+      </c>
+      <c r="E150" s="5" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="F150" s="5" t="inlineStr">
+        <is>
+          <t>San Francisco</t>
+        </is>
+      </c>
+      <c r="G150" s="5" t="inlineStr">
+        <is>
+          <t>Police: 911, Ambulance: 911, Fire: 911</t>
+        </is>
+      </c>
+      <c r="H150" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I150" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J150" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K150" s="5" t="inlineStr"/>
+    </row>
+    <row r="151">
+      <c r="A151" s="5" t="n">
+        <v>141</v>
+      </c>
+      <c r="B151" s="5" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="C151" s="5" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="D151" s="5" t="inlineStr">
+        <is>
+          <t>California</t>
+        </is>
+      </c>
+      <c r="E151" s="5" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="F151" s="5" t="inlineStr">
+        <is>
+          <t>San Jose</t>
+        </is>
+      </c>
+      <c r="G151" s="5" t="inlineStr">
+        <is>
+          <t>Police: 911, Ambulance: 911, Fire: 911</t>
+        </is>
+      </c>
+      <c r="H151" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="I151" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="J151" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="K151" s="5" t="inlineStr"/>
+    </row>
+    <row r="152">
+      <c r="A152" s="5" t="n">
+        <v>142</v>
+      </c>
+      <c r="B152" s="5" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="C152" s="5" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="D152" s="5" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="E152" s="5" t="inlineStr">
+        <is>
+          <t>NY</t>
+        </is>
+      </c>
+      <c r="F152" s="5" t="inlineStr">
+        <is>
+          <t>Buffalo</t>
+        </is>
+      </c>
+      <c r="G152" s="5" t="inlineStr">
+        <is>
+          <t>Police: 911, Ambulance: 911, Fire: 911</t>
+        </is>
+      </c>
+      <c r="H152" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="I152" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="J152" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="K152" s="5" t="inlineStr"/>
+    </row>
+    <row r="153">
+      <c r="A153" s="5" t="n">
+        <v>143</v>
+      </c>
+      <c r="B153" s="5" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="C153" s="5" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="D153" s="5" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="E153" s="5" t="inlineStr">
+        <is>
+          <t>NY</t>
+        </is>
+      </c>
+      <c r="F153" s="5" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="G153" s="5" t="inlineStr">
+        <is>
+          <t>Police: 911, Ambulance: 911, Fire: 911</t>
+        </is>
+      </c>
+      <c r="H153" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="I153" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="J153" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="K153" s="5" t="inlineStr"/>
+    </row>
+    <row r="154">
+      <c r="A154" s="4" t="inlineStr">
+        <is>
+          <t>SECTION 7: Edge Cases</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="5" t="n">
+        <v>144</v>
+      </c>
+      <c r="B155" s="5" t="inlineStr">
+        <is>
+          <t>Unknown country code</t>
+        </is>
+      </c>
+      <c r="C155" s="5" t="inlineStr">
+        <is>
+          <t>XX</t>
+        </is>
+      </c>
+      <c r="D155" s="5" t="inlineStr"/>
+      <c r="E155" s="5" t="inlineStr"/>
+      <c r="F155" s="5" t="inlineStr"/>
+      <c r="G155" s="5" t="inlineStr">
+        <is>
+          <t>Should show error or fallback</t>
+        </is>
+      </c>
+      <c r="H155" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="I155" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="J155" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="K155" s="5" t="inlineStr"/>
+    </row>
+    <row r="156">
+      <c r="A156" s="5" t="n">
+        <v>145</v>
+      </c>
+      <c r="B156" s="5" t="inlineStr">
+        <is>
+          <t>Missing location data</t>
+        </is>
+      </c>
+      <c r="C156" s="5" t="inlineStr"/>
+      <c r="D156" s="5" t="inlineStr"/>
+      <c r="E156" s="5" t="inlineStr"/>
+      <c r="F156" s="5" t="inlineStr"/>
+      <c r="G156" s="5" t="inlineStr">
+        <is>
+          <t>Page should not crash</t>
+        </is>
+      </c>
+      <c r="H156" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="I156" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="J156" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="K156" s="5" t="inlineStr"/>
+    </row>
+    <row r="157">
+      <c r="A157" s="5" t="n">
+        <v>146</v>
+      </c>
+      <c r="B157" s="5" t="inlineStr">
+        <is>
+          <t>Country with no state data</t>
+        </is>
+      </c>
+      <c r="C157" s="5" t="inlineStr">
+        <is>
+          <t>AF</t>
+        </is>
+      </c>
+      <c r="D157" s="5" t="inlineStr">
+        <is>
+          <t>Afghanistan</t>
+        </is>
+      </c>
+      <c r="E157" s="5" t="inlineStr"/>
+      <c r="F157" s="5" t="inlineStr"/>
+      <c r="G157" s="5" t="inlineStr">
+        <is>
           <t>Should fall back to country default</t>
         </is>
       </c>
-      <c r="H63" s="5" t="inlineStr"/>
-      <c r="I63" s="5" t="inlineStr"/>
-      <c r="J63" s="5" t="inlineStr"/>
-      <c r="K63" s="5" t="inlineStr"/>
+      <c r="H157" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="I157" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="J157" s="5" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+      <c r="K157" s="5" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A4:K63"/>
+  <autoFilter ref="A4:K157"/>
   <mergeCells count="9">
-    <mergeCell ref="A53:K53"/>
-    <mergeCell ref="A26:K26"/>
-    <mergeCell ref="A30:K30"/>
-    <mergeCell ref="A38:K38"/>
+    <mergeCell ref="A91:K91"/>
+    <mergeCell ref="A83:K83"/>
+    <mergeCell ref="A146:K146"/>
+    <mergeCell ref="A153:K153"/>
+    <mergeCell ref="A95:K95"/>
     <mergeCell ref="A2:K2"/>
-    <mergeCell ref="A42:K42"/>
-    <mergeCell ref="A60:K60"/>
     <mergeCell ref="A5:K5"/>
     <mergeCell ref="A1:K1"/>
+    <mergeCell ref="A79:K79"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
